--- a/outputs/barcelona_samples_2015_2023_joined_results_20251103.xlsx
+++ b/outputs/barcelona_samples_2015_2023_joined_results_20251103.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="ADD_evt" sheetId="1" state="visible" r:id="rId3"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2147" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2143" uniqueCount="263">
   <si>
     <t xml:space="preserve">2023</t>
   </si>
@@ -793,12 +793,33 @@
     <t xml:space="preserve">Paint on road indicating bike presence, both years..</t>
   </si>
   <si>
-    <t xml:space="preserve">coders_match</t>
+    <t xml:space="preserve">evt_present_followup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evt_present_baseline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evt_match</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vgp_present_followup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vgp_present_baseline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vgp_match</t>
+  </si>
+  <si>
+    <t xml:space="preserve">agreement</t>
   </si>
   <si>
     <t xml:space="preserve">same_result</t>
   </si>
   <si>
+    <t xml:space="preserve">consensus</t>
+  </si>
+  <si>
     <t xml:space="preserve">joined_result</t>
   </si>
   <si>
@@ -812,12 +833,6 @@
   </si>
   <si>
     <t xml:space="preserve">The same case but the point is too far to see if there is or not a bike lane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Initial agreement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Match sources</t>
   </si>
   <si>
     <t xml:space="preserve">We agreed this is not a proper bike lane, it does n´t include any signaling</t>
@@ -827,11 +842,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
     <numFmt numFmtId="166" formatCode="General"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
+    <numFmt numFmtId="168" formatCode="&quot;TRUE&quot;;&quot;TRUE&quot;;&quot;FALSE&quot;"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -999,7 +1015,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1084,8 +1100,8 @@
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -1093,6 +1109,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -12886,30 +12906,24 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:XFD53"/>
+  <dimension ref="A1:S52"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.79"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="5.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="4" style="1" width="0.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="15.62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="12.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="13.81"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10.66"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="5" min="4" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="6" min="6" style="1" width="0.71"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="7" min="7" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="10.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="9" style="1" width="15.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="12.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="12.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="10.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="11.31"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0"/>
-      <c r="C1" s="0"/>
-      <c r="H1" s="0"/>
-      <c r="I1" s="0"/>
-      <c r="J1" s="0"/>
-      <c r="K1" s="0"/>
-      <c r="L1" s="0"/>
-      <c r="XFD1" s="0"/>
-    </row>
+    <row r="1" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="2" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="20" t="s">
         <v>2</v>
@@ -12935,16 +12949,36 @@
       <c r="H2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="20" t="s">
+      <c r="I2" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="J2" s="20" t="s">
+      <c r="J2" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="K2" s="20" t="s">
+      <c r="K2" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="XFD2" s="0"/>
+      <c r="L2" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="O2" s="20" t="s">
+        <v>254</v>
+      </c>
+      <c r="P2" s="20" t="s">
+        <v>255</v>
+      </c>
+      <c r="Q2" s="20" t="s">
+        <v>256</v>
+      </c>
+      <c r="R2" s="20" t="s">
+        <v>257</v>
+      </c>
     </row>
     <row r="3" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="n">
@@ -12973,19 +13007,46 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3909679997347,2.11211089874738","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I3" s="10" t="n">
-        <f aca="false">IF(ADD_evt!R3=ADD_vgp!R3,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J3" s="21" t="b">
-        <f aca="false">IF(I3=1, ADD_evt!R3, "")</f>
-        <v>1</v>
+      <c r="I3" s="3" t="str">
+        <f aca="false">ADD_evt!P3</f>
+        <v>1</v>
+      </c>
+      <c r="J3" s="3" t="str">
+        <f aca="false">ADD_evt!Q3</f>
+        <v>0</v>
       </c>
       <c r="K3" s="21" t="b">
-        <f aca="false">IF(I3=1, ADD_evt!R3, "")</f>
-        <v>1</v>
-      </c>
-      <c r="XFD3" s="0"/>
+        <f aca="false">ADD_evt!R3</f>
+        <v>1</v>
+      </c>
+      <c r="L3" s="3" t="str">
+        <f aca="false">ADD_vgp!P3</f>
+        <v>1</v>
+      </c>
+      <c r="M3" s="3" t="str">
+        <f aca="false">ADD_vgp!Q3</f>
+        <v>0</v>
+      </c>
+      <c r="N3" s="21" t="b">
+        <f aca="false">ADD_vgp!R3</f>
+        <v>1</v>
+      </c>
+      <c r="O3" s="10" t="n">
+        <f aca="false">IF(K3=N3,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P3" s="1" t="n">
+        <f aca="false">IF(O3=1,N(N3),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R3" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P3), ISERROR(Q3), P3="NA", Q3="NA"),
+   "NA",
+   N(P3) + N(Q3)
+)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="4" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="n">
@@ -13014,19 +13075,46 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4581456267453,2.18031012416","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I4" s="10" t="n">
-        <f aca="false">IF(ADD_evt!R4=ADD_vgp!R4,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J4" s="21" t="b">
-        <f aca="false">IF(I4=1, ADD_evt!R4, "")</f>
-        <v>0</v>
-      </c>
-      <c r="K4" s="21" t="b">
-        <f aca="false">IF(I4=1, ADD_evt!R4, "")</f>
-        <v>0</v>
-      </c>
-      <c r="XFD4" s="0"/>
+      <c r="I4" s="3" t="str">
+        <f aca="false">ADD_evt!P4</f>
+        <v>1</v>
+      </c>
+      <c r="J4" s="3" t="str">
+        <f aca="false">ADD_evt!Q4</f>
+        <v>1</v>
+      </c>
+      <c r="K4" s="21" t="n">
+        <f aca="false">ADD_evt!R4</f>
+        <v>0</v>
+      </c>
+      <c r="L4" s="3" t="str">
+        <f aca="false">ADD_vgp!P4</f>
+        <v>1</v>
+      </c>
+      <c r="M4" s="3" t="str">
+        <f aca="false">ADD_vgp!Q4</f>
+        <v>1</v>
+      </c>
+      <c r="N4" s="21" t="n">
+        <f aca="false">ADD_vgp!R4</f>
+        <v>0</v>
+      </c>
+      <c r="O4" s="10" t="n">
+        <f aca="false">IF(K4=N4,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P4" s="1" t="n">
+        <f aca="false">IF(O4=1,N(N4),"")</f>
+        <v>0</v>
+      </c>
+      <c r="R4" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P4), ISERROR(Q4), P4="NA", Q4="NA"),
+   "NA",
+   N(P4) + N(Q4)
+)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="5" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="n">
@@ -13055,19 +13143,46 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4134215995416,2.14085269668676","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I5" s="10" t="n">
-        <f aca="false">IF(ADD_evt!R5=ADD_vgp!R5,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J5" s="21" t="b">
-        <f aca="false">IF(I5=1, ADD_evt!R5, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K5" s="21" t="b">
-        <f aca="false">IF(I5=1, ADD_evt!R5, "")</f>
-        <v>1</v>
-      </c>
-      <c r="XFD5" s="0"/>
+      <c r="I5" s="3" t="str">
+        <f aca="false">ADD_evt!P5</f>
+        <v>1</v>
+      </c>
+      <c r="J5" s="3" t="str">
+        <f aca="false">ADD_evt!Q5</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="21" t="n">
+        <f aca="false">ADD_evt!R5</f>
+        <v>1</v>
+      </c>
+      <c r="L5" s="3" t="str">
+        <f aca="false">ADD_vgp!P5</f>
+        <v>1</v>
+      </c>
+      <c r="M5" s="3" t="str">
+        <f aca="false">ADD_vgp!Q5</f>
+        <v>0</v>
+      </c>
+      <c r="N5" s="21" t="n">
+        <f aca="false">ADD_vgp!R5</f>
+        <v>1</v>
+      </c>
+      <c r="O5" s="10" t="n">
+        <f aca="false">IF(K5=N5,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P5" s="1" t="n">
+        <f aca="false">IF(O5=1,N(N5),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R5" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P5), ISERROR(Q5), P5="NA", Q5="NA"),
+   "NA",
+   N(P5) + N(Q5)
+)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="6" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="n">
@@ -13096,19 +13211,46 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4262832087554,2.20113165987653","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I6" s="10" t="n">
-        <f aca="false">IF(ADD_evt!R6=ADD_vgp!R6,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J6" s="21" t="b">
-        <f aca="false">IF(I6=1, ADD_evt!R6, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K6" s="21" t="b">
-        <f aca="false">IF(I6=1, ADD_evt!R6, "")</f>
-        <v>1</v>
-      </c>
-      <c r="XFD6" s="0"/>
+      <c r="I6" s="3" t="str">
+        <f aca="false">ADD_evt!P6</f>
+        <v>1</v>
+      </c>
+      <c r="J6" s="3" t="str">
+        <f aca="false">ADD_evt!Q6</f>
+        <v>0</v>
+      </c>
+      <c r="K6" s="21" t="n">
+        <f aca="false">ADD_evt!R6</f>
+        <v>1</v>
+      </c>
+      <c r="L6" s="3" t="str">
+        <f aca="false">ADD_vgp!P6</f>
+        <v>1</v>
+      </c>
+      <c r="M6" s="3" t="str">
+        <f aca="false">ADD_vgp!Q6</f>
+        <v>0</v>
+      </c>
+      <c r="N6" s="21" t="n">
+        <f aca="false">ADD_vgp!R6</f>
+        <v>1</v>
+      </c>
+      <c r="O6" s="10" t="n">
+        <f aca="false">IF(K6=N6,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P6" s="1" t="n">
+        <f aca="false">IF(O6=1,N(N6),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R6" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P6), ISERROR(Q6), P6="NA", Q6="NA"),
+   "NA",
+   N(P6) + N(Q6)
+)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="7" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="n">
@@ -13137,19 +13279,46 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4260327049088,2.2001190522901","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I7" s="10" t="n">
-        <f aca="false">IF(ADD_evt!R7=ADD_vgp!R7,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J7" s="21" t="b">
-        <f aca="false">IF(I7=1, ADD_evt!R7, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K7" s="21" t="b">
-        <f aca="false">IF(I7=1, ADD_evt!R7, "")</f>
-        <v>1</v>
-      </c>
-      <c r="XFD7" s="0"/>
+      <c r="I7" s="3" t="str">
+        <f aca="false">ADD_evt!P7</f>
+        <v>1</v>
+      </c>
+      <c r="J7" s="3" t="str">
+        <f aca="false">ADD_evt!Q7</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="21" t="n">
+        <f aca="false">ADD_evt!R7</f>
+        <v>1</v>
+      </c>
+      <c r="L7" s="3" t="str">
+        <f aca="false">ADD_vgp!P7</f>
+        <v>1</v>
+      </c>
+      <c r="M7" s="3" t="str">
+        <f aca="false">ADD_vgp!Q7</f>
+        <v>0</v>
+      </c>
+      <c r="N7" s="21" t="n">
+        <f aca="false">ADD_vgp!R7</f>
+        <v>1</v>
+      </c>
+      <c r="O7" s="10" t="n">
+        <f aca="false">IF(K7=N7,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P7" s="1" t="n">
+        <f aca="false">IF(O7=1,N(N7),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R7" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P7), ISERROR(Q7), P7="NA", Q7="NA"),
+   "NA",
+   N(P7) + N(Q7)
+)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="8" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="n">
@@ -13178,19 +13347,46 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3899636143591,2.134757401236","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I8" s="10" t="n">
-        <f aca="false">IF(ADD_evt!R8=ADD_vgp!R8,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J8" s="21" t="b">
-        <f aca="false">IF(I8=1, ADD_evt!R8, "")</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="21" t="b">
-        <f aca="false">IF(I8=1, ADD_evt!R8, "")</f>
-        <v>0</v>
-      </c>
-      <c r="XFD8" s="0"/>
+      <c r="I8" s="3" t="str">
+        <f aca="false">ADD_evt!P8</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="str">
+        <f aca="false">ADD_evt!Q8</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="21" t="n">
+        <f aca="false">ADD_evt!R8</f>
+        <v>0</v>
+      </c>
+      <c r="L8" s="3" t="str">
+        <f aca="false">ADD_vgp!P8</f>
+        <v>0</v>
+      </c>
+      <c r="M8" s="3" t="str">
+        <f aca="false">ADD_vgp!Q8</f>
+        <v>0</v>
+      </c>
+      <c r="N8" s="21" t="n">
+        <f aca="false">ADD_vgp!R8</f>
+        <v>0</v>
+      </c>
+      <c r="O8" s="10" t="n">
+        <f aca="false">IF(K8=N8,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P8" s="1" t="n">
+        <f aca="false">IF(O8=1,N(N8),"")</f>
+        <v>0</v>
+      </c>
+      <c r="R8" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P8), ISERROR(Q8), P8="NA", Q8="NA"),
+   "NA",
+   N(P8) + N(Q8)
+)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="9" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="n">
@@ -13219,19 +13415,46 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3881854073843,2.13402755812854","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I9" s="10" t="n">
-        <f aca="false">IF(ADD_evt!R9=ADD_vgp!R9,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J9" s="21" t="b">
-        <f aca="false">IF(I9=1, ADD_evt!R9, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K9" s="21" t="b">
-        <f aca="false">IF(I9=1, ADD_evt!R9, "")</f>
-        <v>1</v>
-      </c>
-      <c r="XFD9" s="0"/>
+      <c r="I9" s="3" t="str">
+        <f aca="false">ADD_evt!P9</f>
+        <v>1</v>
+      </c>
+      <c r="J9" s="3" t="str">
+        <f aca="false">ADD_evt!Q9</f>
+        <v>0</v>
+      </c>
+      <c r="K9" s="21" t="n">
+        <f aca="false">ADD_evt!R9</f>
+        <v>1</v>
+      </c>
+      <c r="L9" s="3" t="str">
+        <f aca="false">ADD_vgp!P9</f>
+        <v>1</v>
+      </c>
+      <c r="M9" s="3" t="str">
+        <f aca="false">ADD_vgp!Q9</f>
+        <v>0</v>
+      </c>
+      <c r="N9" s="21" t="n">
+        <f aca="false">ADD_vgp!R9</f>
+        <v>1</v>
+      </c>
+      <c r="O9" s="10" t="n">
+        <f aca="false">IF(K9=N9,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P9" s="1" t="n">
+        <f aca="false">IF(O9=1,N(N9),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R9" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P9), ISERROR(Q9), P9="NA", Q9="NA"),
+   "NA",
+   N(P9) + N(Q9)
+)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="10" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="n">
@@ -13260,19 +13483,46 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4168121764961,2.19881673887713","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I10" s="10" t="n">
-        <f aca="false">IF(ADD_evt!R10=ADD_vgp!R10,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J10" s="21" t="b">
-        <f aca="false">IF(I10=1, ADD_evt!R10, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K10" s="21" t="b">
-        <f aca="false">IF(I10=1, ADD_evt!R10, "")</f>
-        <v>1</v>
-      </c>
-      <c r="XFD10" s="0"/>
+      <c r="I10" s="3" t="str">
+        <f aca="false">ADD_evt!P10</f>
+        <v>1</v>
+      </c>
+      <c r="J10" s="3" t="str">
+        <f aca="false">ADD_evt!Q10</f>
+        <v>0</v>
+      </c>
+      <c r="K10" s="21" t="n">
+        <f aca="false">ADD_evt!R10</f>
+        <v>1</v>
+      </c>
+      <c r="L10" s="3" t="str">
+        <f aca="false">ADD_vgp!P10</f>
+        <v>1</v>
+      </c>
+      <c r="M10" s="3" t="str">
+        <f aca="false">ADD_vgp!Q10</f>
+        <v>0</v>
+      </c>
+      <c r="N10" s="21" t="n">
+        <f aca="false">ADD_vgp!R10</f>
+        <v>1</v>
+      </c>
+      <c r="O10" s="10" t="n">
+        <f aca="false">IF(K10=N10,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P10" s="1" t="n">
+        <f aca="false">IF(O10=1,N(N10),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R10" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P10), ISERROR(Q10), P10="NA", Q10="NA"),
+   "NA",
+   N(P10) + N(Q10)
+)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="11" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="n">
@@ -13301,19 +13551,46 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4168653577514,2.17461017557639","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I11" s="10" t="n">
-        <f aca="false">IF(ADD_evt!R11=ADD_vgp!R11,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J11" s="21" t="b">
-        <f aca="false">IF(I11=1, ADD_evt!R11, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K11" s="21" t="b">
-        <f aca="false">IF(I11=1, ADD_evt!R11, "")</f>
-        <v>1</v>
-      </c>
-      <c r="XFD11" s="0"/>
+      <c r="I11" s="3" t="str">
+        <f aca="false">ADD_evt!P11</f>
+        <v>1</v>
+      </c>
+      <c r="J11" s="3" t="str">
+        <f aca="false">ADD_evt!Q11</f>
+        <v>0</v>
+      </c>
+      <c r="K11" s="21" t="n">
+        <f aca="false">ADD_evt!R11</f>
+        <v>1</v>
+      </c>
+      <c r="L11" s="3" t="str">
+        <f aca="false">ADD_vgp!P11</f>
+        <v>1</v>
+      </c>
+      <c r="M11" s="3" t="str">
+        <f aca="false">ADD_vgp!Q11</f>
+        <v>0</v>
+      </c>
+      <c r="N11" s="21" t="n">
+        <f aca="false">ADD_vgp!R11</f>
+        <v>1</v>
+      </c>
+      <c r="O11" s="10" t="n">
+        <f aca="false">IF(K11=N11,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P11" s="1" t="n">
+        <f aca="false">IF(O11=1,N(N11),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R11" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P11), ISERROR(Q11), P11="NA", Q11="NA"),
+   "NA",
+   N(P11) + N(Q11)
+)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="12" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="n">
@@ -13342,20 +13619,49 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.414975730964,2.17205102853822","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I12" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J12" s="1" t="str">
-        <f aca="false">IF(I12=1, ADD_evt!R12, "")</f>
-        <v/>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="L12" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="XFD12" s="0"/>
+      <c r="I12" s="3" t="str">
+        <f aca="false">ADD_evt!P12</f>
+        <v>NA</v>
+      </c>
+      <c r="J12" s="3" t="str">
+        <f aca="false">ADD_evt!Q12</f>
+        <v>NA</v>
+      </c>
+      <c r="K12" s="21" t="e">
+        <f aca="false">ADD_evt!R12</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L12" s="3" t="str">
+        <f aca="false">ADD_vgp!P12</f>
+        <v>1</v>
+      </c>
+      <c r="M12" s="3" t="str">
+        <f aca="false">ADD_vgp!Q12</f>
+        <v>1</v>
+      </c>
+      <c r="N12" s="21" t="n">
+        <f aca="false">ADD_vgp!R12</f>
+        <v>0</v>
+      </c>
+      <c r="O12" s="10" t="e">
+        <f aca="false">IF(K12=N12,1,0)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P12" s="1" t="e">
+        <f aca="false">IF(O12=1,N(N12),"")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R12" s="1" t="e">
+        <f aca="false">IF(
+   OR(ISERROR(P12), ISERROR(Q12), P12="NA", Q12="NA"),
+   "NA",
+   N(P12) + N(Q12)
+)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S12" s="10" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="13" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="n">
@@ -13384,19 +13690,46 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4204481302083,2.2075546110796","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I13" s="10" t="n">
-        <f aca="false">IF(ADD_evt!R13=ADD_vgp!R13,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J13" s="21" t="b">
-        <f aca="false">IF(I13=1, ADD_evt!R13, "")</f>
-        <v>0</v>
-      </c>
-      <c r="K13" s="21" t="b">
-        <f aca="false">IF(I13=1, ADD_evt!R13, "")</f>
-        <v>0</v>
-      </c>
-      <c r="XFD13" s="0"/>
+      <c r="I13" s="3" t="str">
+        <f aca="false">ADD_evt!P13</f>
+        <v>1</v>
+      </c>
+      <c r="J13" s="3" t="str">
+        <f aca="false">ADD_evt!Q13</f>
+        <v>1</v>
+      </c>
+      <c r="K13" s="21" t="n">
+        <f aca="false">ADD_evt!R13</f>
+        <v>0</v>
+      </c>
+      <c r="L13" s="3" t="str">
+        <f aca="false">ADD_vgp!P13</f>
+        <v>1</v>
+      </c>
+      <c r="M13" s="3" t="str">
+        <f aca="false">ADD_vgp!Q13</f>
+        <v>1</v>
+      </c>
+      <c r="N13" s="21" t="n">
+        <f aca="false">ADD_vgp!R13</f>
+        <v>0</v>
+      </c>
+      <c r="O13" s="10" t="n">
+        <f aca="false">IF(K13=N13,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P13" s="1" t="n">
+        <f aca="false">IF(O13=1,N(N13),"")</f>
+        <v>0</v>
+      </c>
+      <c r="R13" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P13), ISERROR(Q13), P13="NA", Q13="NA"),
+   "NA",
+   N(P13) + N(Q13)
+)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="14" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="n">
@@ -13425,19 +13758,46 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4202454258576,2.20794256929774","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I14" s="10" t="n">
-        <f aca="false">IF(ADD_evt!R14=ADD_vgp!R14,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J14" s="21" t="b">
-        <f aca="false">IF(I14=1, ADD_evt!R14, "")</f>
-        <v>0</v>
-      </c>
-      <c r="K14" s="21" t="b">
-        <f aca="false">IF(I14=1, ADD_evt!R14, "")</f>
-        <v>0</v>
-      </c>
-      <c r="XFD14" s="0"/>
+      <c r="I14" s="3" t="str">
+        <f aca="false">ADD_evt!P14</f>
+        <v>1</v>
+      </c>
+      <c r="J14" s="3" t="str">
+        <f aca="false">ADD_evt!Q14</f>
+        <v>1</v>
+      </c>
+      <c r="K14" s="21" t="n">
+        <f aca="false">ADD_evt!R14</f>
+        <v>0</v>
+      </c>
+      <c r="L14" s="3" t="str">
+        <f aca="false">ADD_vgp!P14</f>
+        <v>1</v>
+      </c>
+      <c r="M14" s="3" t="str">
+        <f aca="false">ADD_vgp!Q14</f>
+        <v>1</v>
+      </c>
+      <c r="N14" s="21" t="n">
+        <f aca="false">ADD_vgp!R14</f>
+        <v>0</v>
+      </c>
+      <c r="O14" s="10" t="n">
+        <f aca="false">IF(K14=N14,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P14" s="1" t="n">
+        <f aca="false">IF(O14=1,N(N14),"")</f>
+        <v>0</v>
+      </c>
+      <c r="R14" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P14), ISERROR(Q14), P14="NA", Q14="NA"),
+   "NA",
+   N(P14) + N(Q14)
+)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="15" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="n">
@@ -13466,19 +13826,46 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4121092794043,2.16098092184219","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I15" s="10" t="n">
-        <f aca="false">IF(ADD_evt!R15=ADD_vgp!R15,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J15" s="21" t="b">
-        <f aca="false">IF(I15=1, ADD_evt!R15, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K15" s="21" t="b">
-        <f aca="false">IF(I15=1, ADD_evt!R15, "")</f>
-        <v>1</v>
-      </c>
-      <c r="XFD15" s="0"/>
+      <c r="I15" s="3" t="str">
+        <f aca="false">ADD_evt!P15</f>
+        <v>1</v>
+      </c>
+      <c r="J15" s="3" t="str">
+        <f aca="false">ADD_evt!Q15</f>
+        <v>0</v>
+      </c>
+      <c r="K15" s="21" t="n">
+        <f aca="false">ADD_evt!R15</f>
+        <v>1</v>
+      </c>
+      <c r="L15" s="3" t="str">
+        <f aca="false">ADD_vgp!P15</f>
+        <v>1</v>
+      </c>
+      <c r="M15" s="3" t="str">
+        <f aca="false">ADD_vgp!Q15</f>
+        <v>0</v>
+      </c>
+      <c r="N15" s="21" t="n">
+        <f aca="false">ADD_vgp!R15</f>
+        <v>1</v>
+      </c>
+      <c r="O15" s="10" t="n">
+        <f aca="false">IF(K15=N15,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P15" s="1" t="n">
+        <f aca="false">IF(O15=1,N(N15),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R15" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P15), ISERROR(Q15), P15="NA", Q15="NA"),
+   "NA",
+   N(P15) + N(Q15)
+)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="16" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="n">
@@ -13507,19 +13894,46 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4125465819168,2.16175831110785","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I16" s="10" t="n">
-        <f aca="false">IF(ADD_evt!R16=ADD_vgp!R16,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J16" s="21" t="b">
-        <f aca="false">IF(I16=1, ADD_evt!R16, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K16" s="21" t="b">
-        <f aca="false">IF(I16=1, ADD_evt!R16, "")</f>
-        <v>1</v>
-      </c>
-      <c r="XFD16" s="0"/>
+      <c r="I16" s="3" t="str">
+        <f aca="false">ADD_evt!P16</f>
+        <v>1</v>
+      </c>
+      <c r="J16" s="3" t="str">
+        <f aca="false">ADD_evt!Q16</f>
+        <v>0</v>
+      </c>
+      <c r="K16" s="21" t="n">
+        <f aca="false">ADD_evt!R16</f>
+        <v>1</v>
+      </c>
+      <c r="L16" s="3" t="str">
+        <f aca="false">ADD_vgp!P16</f>
+        <v>1</v>
+      </c>
+      <c r="M16" s="3" t="str">
+        <f aca="false">ADD_vgp!Q16</f>
+        <v>0</v>
+      </c>
+      <c r="N16" s="21" t="n">
+        <f aca="false">ADD_vgp!R16</f>
+        <v>1</v>
+      </c>
+      <c r="O16" s="10" t="n">
+        <f aca="false">IF(K16=N16,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P16" s="1" t="n">
+        <f aca="false">IF(O16=1,N(N16),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R16" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P16), ISERROR(Q16), P16="NA", Q16="NA"),
+   "NA",
+   N(P16) + N(Q16)
+)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="17" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="n">
@@ -13548,19 +13962,46 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3945206907087,2.20077256303846","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I17" s="10" t="n">
-        <f aca="false">IF(ADD_evt!R17=ADD_vgp!R17,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J17" s="21" t="b">
-        <f aca="false">IF(I17=1, ADD_evt!R17, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K17" s="21" t="b">
-        <f aca="false">IF(I17=1, ADD_evt!R17, "")</f>
-        <v>1</v>
-      </c>
-      <c r="XFD17" s="0"/>
+      <c r="I17" s="3" t="str">
+        <f aca="false">ADD_evt!P17</f>
+        <v>1</v>
+      </c>
+      <c r="J17" s="3" t="str">
+        <f aca="false">ADD_evt!Q17</f>
+        <v>0</v>
+      </c>
+      <c r="K17" s="21" t="n">
+        <f aca="false">ADD_evt!R17</f>
+        <v>1</v>
+      </c>
+      <c r="L17" s="3" t="str">
+        <f aca="false">ADD_vgp!P17</f>
+        <v>1</v>
+      </c>
+      <c r="M17" s="3" t="str">
+        <f aca="false">ADD_vgp!Q17</f>
+        <v>0</v>
+      </c>
+      <c r="N17" s="21" t="n">
+        <f aca="false">ADD_vgp!R17</f>
+        <v>1</v>
+      </c>
+      <c r="O17" s="10" t="n">
+        <f aca="false">IF(K17=N17,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P17" s="1" t="n">
+        <f aca="false">IF(O17=1,N(N17),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R17" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P17), ISERROR(Q17), P17="NA", Q17="NA"),
+   "NA",
+   N(P17) + N(Q17)
+)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="18" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="n">
@@ -13589,19 +14030,46 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.394718915396,2.20100922656311","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I18" s="10" t="n">
-        <f aca="false">IF(ADD_evt!R18=ADD_vgp!R18,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J18" s="21" t="b">
-        <f aca="false">IF(I18=1, ADD_evt!R18, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K18" s="21" t="b">
-        <f aca="false">IF(I18=1, ADD_evt!R18, "")</f>
-        <v>1</v>
-      </c>
-      <c r="XFD18" s="0"/>
+      <c r="I18" s="3" t="str">
+        <f aca="false">ADD_evt!P18</f>
+        <v>1</v>
+      </c>
+      <c r="J18" s="3" t="str">
+        <f aca="false">ADD_evt!Q18</f>
+        <v>0</v>
+      </c>
+      <c r="K18" s="21" t="n">
+        <f aca="false">ADD_evt!R18</f>
+        <v>1</v>
+      </c>
+      <c r="L18" s="3" t="str">
+        <f aca="false">ADD_vgp!P18</f>
+        <v>1</v>
+      </c>
+      <c r="M18" s="3" t="str">
+        <f aca="false">ADD_vgp!Q18</f>
+        <v>0</v>
+      </c>
+      <c r="N18" s="21" t="n">
+        <f aca="false">ADD_vgp!R18</f>
+        <v>1</v>
+      </c>
+      <c r="O18" s="10" t="n">
+        <f aca="false">IF(K18=N18,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P18" s="1" t="n">
+        <f aca="false">IF(O18=1,N(N18),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R18" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P18), ISERROR(Q18), P18="NA", Q18="NA"),
+   "NA",
+   N(P18) + N(Q18)
+)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="19" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="n">
@@ -13630,19 +14098,46 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3762241357195,2.14515055931621","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I19" s="10" t="n">
-        <f aca="false">IF(ADD_evt!R19=ADD_vgp!R19,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J19" s="21" t="b">
-        <f aca="false">IF(I19=1, ADD_evt!R19, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K19" s="21" t="b">
-        <f aca="false">IF(I19=1, ADD_evt!R19, "")</f>
-        <v>1</v>
-      </c>
-      <c r="XFD19" s="0"/>
+      <c r="I19" s="3" t="str">
+        <f aca="false">ADD_evt!P19</f>
+        <v>1</v>
+      </c>
+      <c r="J19" s="3" t="str">
+        <f aca="false">ADD_evt!Q19</f>
+        <v>0</v>
+      </c>
+      <c r="K19" s="21" t="n">
+        <f aca="false">ADD_evt!R19</f>
+        <v>1</v>
+      </c>
+      <c r="L19" s="3" t="str">
+        <f aca="false">ADD_vgp!P19</f>
+        <v>1</v>
+      </c>
+      <c r="M19" s="3" t="str">
+        <f aca="false">ADD_vgp!Q19</f>
+        <v>0</v>
+      </c>
+      <c r="N19" s="21" t="n">
+        <f aca="false">ADD_vgp!R19</f>
+        <v>1</v>
+      </c>
+      <c r="O19" s="10" t="n">
+        <f aca="false">IF(K19=N19,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P19" s="1" t="n">
+        <f aca="false">IF(O19=1,N(N19),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R19" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P19), ISERROR(Q19), P19="NA", Q19="NA"),
+   "NA",
+   N(P19) + N(Q19)
+)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="20" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="n">
@@ -13671,19 +14166,46 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3764134914288,2.14559167922172","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I20" s="10" t="n">
-        <f aca="false">IF(ADD_evt!R20=ADD_vgp!R20,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J20" s="21" t="b">
-        <f aca="false">IF(I20=1, ADD_evt!R20, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K20" s="21" t="b">
-        <f aca="false">IF(I20=1, ADD_evt!R20, "")</f>
-        <v>1</v>
-      </c>
-      <c r="XFD20" s="0"/>
+      <c r="I20" s="3" t="str">
+        <f aca="false">ADD_evt!P20</f>
+        <v>1</v>
+      </c>
+      <c r="J20" s="3" t="str">
+        <f aca="false">ADD_evt!Q20</f>
+        <v>0</v>
+      </c>
+      <c r="K20" s="21" t="n">
+        <f aca="false">ADD_evt!R20</f>
+        <v>1</v>
+      </c>
+      <c r="L20" s="3" t="str">
+        <f aca="false">ADD_vgp!P20</f>
+        <v>1</v>
+      </c>
+      <c r="M20" s="3" t="str">
+        <f aca="false">ADD_vgp!Q20</f>
+        <v>0</v>
+      </c>
+      <c r="N20" s="21" t="n">
+        <f aca="false">ADD_vgp!R20</f>
+        <v>1</v>
+      </c>
+      <c r="O20" s="10" t="n">
+        <f aca="false">IF(K20=N20,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P20" s="1" t="n">
+        <f aca="false">IF(O20=1,N(N20),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R20" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P20), ISERROR(Q20), P20="NA", Q20="NA"),
+   "NA",
+   N(P20) + N(Q20)
+)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="21" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="n">
@@ -13712,19 +14234,46 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4055753756871,2.18284748138898","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I21" s="10" t="n">
-        <f aca="false">IF(ADD_evt!R21=ADD_vgp!R21,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J21" s="21" t="b">
-        <f aca="false">IF(I21=1, ADD_evt!R21, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K21" s="21" t="b">
-        <f aca="false">IF(I21=1, ADD_evt!R21, "")</f>
-        <v>1</v>
-      </c>
-      <c r="XFD21" s="0"/>
+      <c r="I21" s="3" t="str">
+        <f aca="false">ADD_evt!P21</f>
+        <v>1</v>
+      </c>
+      <c r="J21" s="3" t="str">
+        <f aca="false">ADD_evt!Q21</f>
+        <v>0</v>
+      </c>
+      <c r="K21" s="21" t="n">
+        <f aca="false">ADD_evt!R21</f>
+        <v>1</v>
+      </c>
+      <c r="L21" s="3" t="str">
+        <f aca="false">ADD_vgp!P21</f>
+        <v>1</v>
+      </c>
+      <c r="M21" s="3" t="str">
+        <f aca="false">ADD_vgp!Q21</f>
+        <v>0</v>
+      </c>
+      <c r="N21" s="21" t="n">
+        <f aca="false">ADD_vgp!R21</f>
+        <v>1</v>
+      </c>
+      <c r="O21" s="10" t="n">
+        <f aca="false">IF(K21=N21,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P21" s="1" t="n">
+        <f aca="false">IF(O21=1,N(N21),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R21" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P21), ISERROR(Q21), P21="NA", Q21="NA"),
+   "NA",
+   N(P21) + N(Q21)
+)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="22" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="10" t="n">
@@ -13753,19 +14302,46 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.403094880684,2.18285971742863","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I22" s="10" t="n">
-        <f aca="false">IF(ADD_evt!R22=ADD_vgp!R22,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J22" s="21" t="b">
-        <f aca="false">IF(I22=1, ADD_evt!R22, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K22" s="21" t="b">
-        <f aca="false">IF(I22=1, ADD_evt!R22, "")</f>
-        <v>1</v>
-      </c>
-      <c r="XFD22" s="0"/>
+      <c r="I22" s="3" t="str">
+        <f aca="false">ADD_evt!P22</f>
+        <v>1</v>
+      </c>
+      <c r="J22" s="3" t="str">
+        <f aca="false">ADD_evt!Q22</f>
+        <v>0</v>
+      </c>
+      <c r="K22" s="21" t="n">
+        <f aca="false">ADD_evt!R22</f>
+        <v>1</v>
+      </c>
+      <c r="L22" s="3" t="str">
+        <f aca="false">ADD_vgp!P22</f>
+        <v>1</v>
+      </c>
+      <c r="M22" s="3" t="str">
+        <f aca="false">ADD_vgp!Q22</f>
+        <v>0</v>
+      </c>
+      <c r="N22" s="21" t="n">
+        <f aca="false">ADD_vgp!R22</f>
+        <v>1</v>
+      </c>
+      <c r="O22" s="10" t="n">
+        <f aca="false">IF(K22=N22,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P22" s="1" t="n">
+        <f aca="false">IF(O22=1,N(N22),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R22" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P22), ISERROR(Q22), P22="NA", Q22="NA"),
+   "NA",
+   N(P22) + N(Q22)
+)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="23" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="n">
@@ -13794,19 +14370,46 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4287555466715,2.17585558557915","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I23" s="10" t="n">
-        <f aca="false">IF(ADD_evt!R23=ADD_vgp!R23,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J23" s="21" t="b">
-        <f aca="false">IF(I23=1, ADD_evt!R23, "")</f>
-        <v>0</v>
-      </c>
-      <c r="K23" s="21" t="b">
-        <f aca="false">IF(I23=1, ADD_evt!R23, "")</f>
-        <v>0</v>
-      </c>
-      <c r="XFD23" s="0"/>
+      <c r="I23" s="3" t="str">
+        <f aca="false">ADD_evt!P23</f>
+        <v>1</v>
+      </c>
+      <c r="J23" s="3" t="str">
+        <f aca="false">ADD_evt!Q23</f>
+        <v>1</v>
+      </c>
+      <c r="K23" s="21" t="n">
+        <f aca="false">ADD_evt!R23</f>
+        <v>0</v>
+      </c>
+      <c r="L23" s="3" t="str">
+        <f aca="false">ADD_vgp!P23</f>
+        <v>1</v>
+      </c>
+      <c r="M23" s="3" t="str">
+        <f aca="false">ADD_vgp!Q23</f>
+        <v>1</v>
+      </c>
+      <c r="N23" s="21" t="n">
+        <f aca="false">ADD_vgp!R23</f>
+        <v>0</v>
+      </c>
+      <c r="O23" s="10" t="n">
+        <f aca="false">IF(K23=N23,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P23" s="1" t="n">
+        <f aca="false">IF(O23=1,N(N23),"")</f>
+        <v>0</v>
+      </c>
+      <c r="R23" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P23), ISERROR(Q23), P23="NA", Q23="NA"),
+   "NA",
+   N(P23) + N(Q23)
+)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="24" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="10" t="n">
@@ -13835,19 +14438,46 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4409954760919,2.19083141351904","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I24" s="10" t="n">
-        <f aca="false">IF(ADD_evt!R24=ADD_vgp!R24,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J24" s="21" t="b">
-        <f aca="false">IF(I24=1, ADD_evt!R24, "")</f>
-        <v>0</v>
-      </c>
-      <c r="K24" s="21" t="b">
-        <f aca="false">IF(I24=1, ADD_evt!R24, "")</f>
-        <v>0</v>
-      </c>
-      <c r="XFD24" s="0"/>
+      <c r="I24" s="3" t="str">
+        <f aca="false">ADD_evt!P24</f>
+        <v>1</v>
+      </c>
+      <c r="J24" s="3" t="str">
+        <f aca="false">ADD_evt!Q24</f>
+        <v>1</v>
+      </c>
+      <c r="K24" s="21" t="n">
+        <f aca="false">ADD_evt!R24</f>
+        <v>0</v>
+      </c>
+      <c r="L24" s="3" t="str">
+        <f aca="false">ADD_vgp!P24</f>
+        <v>1</v>
+      </c>
+      <c r="M24" s="3" t="str">
+        <f aca="false">ADD_vgp!Q24</f>
+        <v>1</v>
+      </c>
+      <c r="N24" s="21" t="n">
+        <f aca="false">ADD_vgp!R24</f>
+        <v>0</v>
+      </c>
+      <c r="O24" s="10" t="n">
+        <f aca="false">IF(K24=N24,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P24" s="1" t="n">
+        <f aca="false">IF(O24=1,N(N24),"")</f>
+        <v>0</v>
+      </c>
+      <c r="R24" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P24), ISERROR(Q24), P24="NA", Q24="NA"),
+   "NA",
+   N(P24) + N(Q24)
+)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="25" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="n">
@@ -13876,19 +14506,46 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4003124653889,2.15155610489397","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I25" s="10" t="n">
-        <f aca="false">IF(ADD_evt!R25=ADD_vgp!R25,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J25" s="21" t="b">
-        <f aca="false">IF(I25=1, ADD_evt!R25, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K25" s="21" t="b">
-        <f aca="false">IF(I25=1, ADD_evt!R25, "")</f>
-        <v>1</v>
-      </c>
-      <c r="XFD25" s="0"/>
+      <c r="I25" s="3" t="str">
+        <f aca="false">ADD_evt!P25</f>
+        <v>1</v>
+      </c>
+      <c r="J25" s="3" t="str">
+        <f aca="false">ADD_evt!Q25</f>
+        <v>0</v>
+      </c>
+      <c r="K25" s="21" t="n">
+        <f aca="false">ADD_evt!R25</f>
+        <v>1</v>
+      </c>
+      <c r="L25" s="3" t="str">
+        <f aca="false">ADD_vgp!P25</f>
+        <v>1</v>
+      </c>
+      <c r="M25" s="3" t="str">
+        <f aca="false">ADD_vgp!Q25</f>
+        <v>0</v>
+      </c>
+      <c r="N25" s="21" t="n">
+        <f aca="false">ADD_vgp!R25</f>
+        <v>1</v>
+      </c>
+      <c r="O25" s="10" t="n">
+        <f aca="false">IF(K25=N25,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P25" s="1" t="n">
+        <f aca="false">IF(O25=1,N(N25),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R25" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P25), ISERROR(Q25), P25="NA", Q25="NA"),
+   "NA",
+   N(P25) + N(Q25)
+)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="26" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="10" t="n">
@@ -13917,19 +14574,46 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.400204647767,2.15153939610418","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I26" s="10" t="n">
-        <f aca="false">IF(ADD_evt!R26=ADD_vgp!R26,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J26" s="21" t="b">
-        <f aca="false">IF(I26=1, ADD_evt!R26, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K26" s="21" t="b">
-        <f aca="false">IF(I26=1, ADD_evt!R26, "")</f>
-        <v>1</v>
-      </c>
-      <c r="XFD26" s="0"/>
+      <c r="I26" s="3" t="str">
+        <f aca="false">ADD_evt!P26</f>
+        <v>1</v>
+      </c>
+      <c r="J26" s="3" t="str">
+        <f aca="false">ADD_evt!Q26</f>
+        <v>0</v>
+      </c>
+      <c r="K26" s="21" t="n">
+        <f aca="false">ADD_evt!R26</f>
+        <v>1</v>
+      </c>
+      <c r="L26" s="3" t="str">
+        <f aca="false">ADD_vgp!P26</f>
+        <v>1</v>
+      </c>
+      <c r="M26" s="3" t="str">
+        <f aca="false">ADD_vgp!Q26</f>
+        <v>0</v>
+      </c>
+      <c r="N26" s="21" t="n">
+        <f aca="false">ADD_vgp!R26</f>
+        <v>1</v>
+      </c>
+      <c r="O26" s="10" t="n">
+        <f aca="false">IF(K26=N26,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P26" s="1" t="n">
+        <f aca="false">IF(O26=1,N(N26),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R26" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P26), ISERROR(Q26), P26="NA", Q26="NA"),
+   "NA",
+   N(P26) + N(Q26)
+)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="27" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="n">
@@ -13958,20 +14642,49 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4130517909949,2.18688350279505","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I27" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J27" s="1" t="str">
-        <f aca="false">IF(I27=1, ADD_evt!R27, "")</f>
-        <v/>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="L27" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="XFD27" s="0"/>
+      <c r="I27" s="3" t="str">
+        <f aca="false">ADD_evt!P27</f>
+        <v>NA</v>
+      </c>
+      <c r="J27" s="3" t="str">
+        <f aca="false">ADD_evt!Q27</f>
+        <v>NA</v>
+      </c>
+      <c r="K27" s="21" t="e">
+        <f aca="false">ADD_evt!R27</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L27" s="3" t="str">
+        <f aca="false">ADD_vgp!P27</f>
+        <v>1</v>
+      </c>
+      <c r="M27" s="3" t="str">
+        <f aca="false">ADD_vgp!Q27</f>
+        <v>0</v>
+      </c>
+      <c r="N27" s="21" t="n">
+        <f aca="false">ADD_vgp!R27</f>
+        <v>1</v>
+      </c>
+      <c r="O27" s="10" t="e">
+        <f aca="false">IF(K27=N27,1,0)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P27" s="1" t="e">
+        <f aca="false">IF(O27=1,N(N27),"")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R27" s="1" t="e">
+        <f aca="false">IF(
+   OR(ISERROR(P27), ISERROR(Q27), P27="NA", Q27="NA"),
+   "NA",
+   N(P27) + N(Q27)
+)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S27" s="10" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="28" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="10" t="n">
@@ -14000,19 +14713,46 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4140408624214,2.18630763816643","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I28" s="10" t="n">
-        <f aca="false">IF(ADD_evt!R28=ADD_vgp!R28,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J28" s="21" t="b">
-        <f aca="false">IF(I28=1, ADD_evt!R28, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K28" s="21" t="b">
-        <f aca="false">IF(I28=1, ADD_evt!R28, "")</f>
-        <v>1</v>
-      </c>
-      <c r="XFD28" s="0"/>
+      <c r="I28" s="3" t="str">
+        <f aca="false">ADD_evt!P28</f>
+        <v>1</v>
+      </c>
+      <c r="J28" s="3" t="str">
+        <f aca="false">ADD_evt!Q28</f>
+        <v>0</v>
+      </c>
+      <c r="K28" s="21" t="n">
+        <f aca="false">ADD_evt!R28</f>
+        <v>1</v>
+      </c>
+      <c r="L28" s="3" t="str">
+        <f aca="false">ADD_vgp!P28</f>
+        <v>1</v>
+      </c>
+      <c r="M28" s="3" t="str">
+        <f aca="false">ADD_vgp!Q28</f>
+        <v>0</v>
+      </c>
+      <c r="N28" s="21" t="n">
+        <f aca="false">ADD_vgp!R28</f>
+        <v>1</v>
+      </c>
+      <c r="O28" s="10" t="n">
+        <f aca="false">IF(K28=N28,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P28" s="1" t="n">
+        <f aca="false">IF(O28=1,N(N28),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R28" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P28), ISERROR(Q28), P28="NA", Q28="NA"),
+   "NA",
+   N(P28) + N(Q28)
+)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="29" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="10" t="n">
@@ -14041,19 +14781,46 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3859805190524,2.13625700853397","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I29" s="10" t="n">
-        <f aca="false">IF(ADD_evt!R29=ADD_vgp!R29,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J29" s="21" t="b">
-        <f aca="false">IF(I29=1, ADD_evt!R29, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K29" s="21" t="b">
-        <f aca="false">IF(I29=1, ADD_evt!R29, "")</f>
-        <v>1</v>
-      </c>
-      <c r="XFD29" s="0"/>
+      <c r="I29" s="3" t="str">
+        <f aca="false">ADD_evt!P29</f>
+        <v>1</v>
+      </c>
+      <c r="J29" s="3" t="str">
+        <f aca="false">ADD_evt!Q29</f>
+        <v>0</v>
+      </c>
+      <c r="K29" s="21" t="n">
+        <f aca="false">ADD_evt!R29</f>
+        <v>1</v>
+      </c>
+      <c r="L29" s="3" t="str">
+        <f aca="false">ADD_vgp!P29</f>
+        <v>1</v>
+      </c>
+      <c r="M29" s="3" t="str">
+        <f aca="false">ADD_vgp!Q29</f>
+        <v>0</v>
+      </c>
+      <c r="N29" s="21" t="n">
+        <f aca="false">ADD_vgp!R29</f>
+        <v>1</v>
+      </c>
+      <c r="O29" s="10" t="n">
+        <f aca="false">IF(K29=N29,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P29" s="1" t="n">
+        <f aca="false">IF(O29=1,N(N29),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R29" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P29), ISERROR(Q29), P29="NA", Q29="NA"),
+   "NA",
+   N(P29) + N(Q29)
+)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="30" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="10" t="n">
@@ -14082,19 +14849,46 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3852971271454,2.13855858286425","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I30" s="10" t="n">
-        <f aca="false">IF(ADD_evt!R30=ADD_vgp!R30,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J30" s="21" t="b">
-        <f aca="false">IF(I30=1, ADD_evt!R30, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K30" s="21" t="b">
-        <f aca="false">IF(I30=1, ADD_evt!R30, "")</f>
-        <v>1</v>
-      </c>
-      <c r="XFD30" s="0"/>
+      <c r="I30" s="3" t="str">
+        <f aca="false">ADD_evt!P30</f>
+        <v>1</v>
+      </c>
+      <c r="J30" s="3" t="str">
+        <f aca="false">ADD_evt!Q30</f>
+        <v>0</v>
+      </c>
+      <c r="K30" s="21" t="n">
+        <f aca="false">ADD_evt!R30</f>
+        <v>1</v>
+      </c>
+      <c r="L30" s="3" t="str">
+        <f aca="false">ADD_vgp!P30</f>
+        <v>1</v>
+      </c>
+      <c r="M30" s="3" t="str">
+        <f aca="false">ADD_vgp!Q30</f>
+        <v>0</v>
+      </c>
+      <c r="N30" s="21" t="n">
+        <f aca="false">ADD_vgp!R30</f>
+        <v>1</v>
+      </c>
+      <c r="O30" s="10" t="n">
+        <f aca="false">IF(K30=N30,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P30" s="1" t="n">
+        <f aca="false">IF(O30=1,N(N30),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R30" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P30), ISERROR(Q30), P30="NA", Q30="NA"),
+   "NA",
+   N(P30) + N(Q30)
+)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="31" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="10" t="n">
@@ -14123,19 +14917,46 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3911878676426,2.18642991571189","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I31" s="10" t="n">
-        <f aca="false">IF(ADD_evt!R31=ADD_vgp!R31,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J31" s="21" t="b">
-        <f aca="false">IF(I31=1, ADD_evt!R31, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K31" s="21" t="b">
-        <f aca="false">IF(I31=1, ADD_evt!R31, "")</f>
-        <v>1</v>
-      </c>
-      <c r="XFD31" s="0"/>
+      <c r="I31" s="3" t="str">
+        <f aca="false">ADD_evt!P31</f>
+        <v>1</v>
+      </c>
+      <c r="J31" s="3" t="str">
+        <f aca="false">ADD_evt!Q31</f>
+        <v>0</v>
+      </c>
+      <c r="K31" s="21" t="n">
+        <f aca="false">ADD_evt!R31</f>
+        <v>1</v>
+      </c>
+      <c r="L31" s="3" t="str">
+        <f aca="false">ADD_vgp!P31</f>
+        <v>1</v>
+      </c>
+      <c r="M31" s="3" t="str">
+        <f aca="false">ADD_vgp!Q31</f>
+        <v>0</v>
+      </c>
+      <c r="N31" s="21" t="n">
+        <f aca="false">ADD_vgp!R31</f>
+        <v>1</v>
+      </c>
+      <c r="O31" s="10" t="n">
+        <f aca="false">IF(K31=N31,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P31" s="1" t="n">
+        <f aca="false">IF(O31=1,N(N31),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R31" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P31), ISERROR(Q31), P31="NA", Q31="NA"),
+   "NA",
+   N(P31) + N(Q31)
+)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="32" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="10" t="n">
@@ -14164,19 +14985,46 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3903749358271,2.18533799661021","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I32" s="10" t="n">
-        <f aca="false">IF(ADD_evt!R32=ADD_vgp!R32,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J32" s="21" t="b">
-        <f aca="false">IF(I32=1, ADD_evt!R32, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K32" s="21" t="b">
-        <f aca="false">IF(I32=1, ADD_evt!R32, "")</f>
-        <v>1</v>
-      </c>
-      <c r="XFD32" s="0"/>
+      <c r="I32" s="3" t="str">
+        <f aca="false">ADD_evt!P32</f>
+        <v>1</v>
+      </c>
+      <c r="J32" s="3" t="str">
+        <f aca="false">ADD_evt!Q32</f>
+        <v>0</v>
+      </c>
+      <c r="K32" s="21" t="n">
+        <f aca="false">ADD_evt!R32</f>
+        <v>1</v>
+      </c>
+      <c r="L32" s="3" t="str">
+        <f aca="false">ADD_vgp!P32</f>
+        <v>1</v>
+      </c>
+      <c r="M32" s="3" t="str">
+        <f aca="false">ADD_vgp!Q32</f>
+        <v>0</v>
+      </c>
+      <c r="N32" s="21" t="n">
+        <f aca="false">ADD_vgp!R32</f>
+        <v>1</v>
+      </c>
+      <c r="O32" s="10" t="n">
+        <f aca="false">IF(K32=N32,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P32" s="1" t="n">
+        <f aca="false">IF(O32=1,N(N32),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R32" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P32), ISERROR(Q32), P32="NA", Q32="NA"),
+   "NA",
+   N(P32) + N(Q32)
+)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="33" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="n">
@@ -14205,20 +15053,49 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3826431790481,2.15897555292766","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I33" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J33" s="1" t="str">
-        <f aca="false">IF(I33=1, ADD_evt!R33, "")</f>
-        <v/>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="L33" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="XFD33" s="0"/>
+      <c r="I33" s="3" t="str">
+        <f aca="false">ADD_evt!P33</f>
+        <v>NA</v>
+      </c>
+      <c r="J33" s="3" t="str">
+        <f aca="false">ADD_evt!Q33</f>
+        <v>NA</v>
+      </c>
+      <c r="K33" s="21" t="e">
+        <f aca="false">ADD_evt!R33</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L33" s="3" t="str">
+        <f aca="false">ADD_vgp!P33</f>
+        <v>1</v>
+      </c>
+      <c r="M33" s="3" t="str">
+        <f aca="false">ADD_vgp!Q33</f>
+        <v>1</v>
+      </c>
+      <c r="N33" s="21" t="n">
+        <f aca="false">ADD_vgp!R33</f>
+        <v>0</v>
+      </c>
+      <c r="O33" s="10" t="e">
+        <f aca="false">IF(K33=N33,1,0)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P33" s="1" t="e">
+        <f aca="false">IF(O33=1,N(N33),"")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R33" s="1" t="e">
+        <f aca="false">IF(
+   OR(ISERROR(P33), ISERROR(Q33), P33="NA", Q33="NA"),
+   "NA",
+   N(P33) + N(Q33)
+)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S33" s="10" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="34" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="10" t="n">
@@ -14247,19 +15124,46 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3981184632183,2.15370501205099","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I34" s="10" t="n">
-        <f aca="false">IF(ADD_evt!R34=ADD_vgp!R34,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J34" s="21" t="b">
-        <f aca="false">IF(I34=1, ADD_evt!R34, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K34" s="21" t="b">
-        <f aca="false">IF(I34=1, ADD_evt!R34, "")</f>
-        <v>1</v>
-      </c>
-      <c r="XFD34" s="0"/>
+      <c r="I34" s="3" t="str">
+        <f aca="false">ADD_evt!P34</f>
+        <v>1</v>
+      </c>
+      <c r="J34" s="3" t="str">
+        <f aca="false">ADD_evt!Q34</f>
+        <v>0</v>
+      </c>
+      <c r="K34" s="21" t="n">
+        <f aca="false">ADD_evt!R34</f>
+        <v>1</v>
+      </c>
+      <c r="L34" s="3" t="str">
+        <f aca="false">ADD_vgp!P34</f>
+        <v>1</v>
+      </c>
+      <c r="M34" s="3" t="str">
+        <f aca="false">ADD_vgp!Q34</f>
+        <v>0</v>
+      </c>
+      <c r="N34" s="21" t="n">
+        <f aca="false">ADD_vgp!R34</f>
+        <v>1</v>
+      </c>
+      <c r="O34" s="10" t="n">
+        <f aca="false">IF(K34=N34,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P34" s="1" t="n">
+        <f aca="false">IF(O34=1,N(N34),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R34" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P34), ISERROR(Q34), P34="NA", Q34="NA"),
+   "NA",
+   N(P34) + N(Q34)
+)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="35" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="10" t="n">
@@ -14288,19 +15192,46 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3981332109611,2.1537501547691","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I35" s="10" t="n">
-        <f aca="false">IF(ADD_evt!R35=ADD_vgp!R35,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J35" s="21" t="b">
-        <f aca="false">IF(I35=1, ADD_evt!R35, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K35" s="21" t="b">
-        <f aca="false">IF(I35=1, ADD_evt!R35, "")</f>
-        <v>1</v>
-      </c>
-      <c r="XFD35" s="0"/>
+      <c r="I35" s="3" t="str">
+        <f aca="false">ADD_evt!P35</f>
+        <v>1</v>
+      </c>
+      <c r="J35" s="3" t="str">
+        <f aca="false">ADD_evt!Q35</f>
+        <v>0</v>
+      </c>
+      <c r="K35" s="21" t="n">
+        <f aca="false">ADD_evt!R35</f>
+        <v>1</v>
+      </c>
+      <c r="L35" s="3" t="str">
+        <f aca="false">ADD_vgp!P35</f>
+        <v>1</v>
+      </c>
+      <c r="M35" s="3" t="str">
+        <f aca="false">ADD_vgp!Q35</f>
+        <v>0</v>
+      </c>
+      <c r="N35" s="21" t="n">
+        <f aca="false">ADD_vgp!R35</f>
+        <v>1</v>
+      </c>
+      <c r="O35" s="10" t="n">
+        <f aca="false">IF(K35=N35,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P35" s="1" t="n">
+        <f aca="false">IF(O35=1,N(N35),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R35" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P35), ISERROR(Q35), P35="NA", Q35="NA"),
+   "NA",
+   N(P35) + N(Q35)
+)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="36" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="10" t="n">
@@ -14329,19 +15260,46 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3756644128399,2.1240095291374","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I36" s="10" t="n">
-        <f aca="false">IF(ADD_evt!R36=ADD_vgp!R36,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J36" s="21" t="b">
-        <f aca="false">IF(I36=1, ADD_evt!R36, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K36" s="21" t="b">
-        <f aca="false">IF(I36=1, ADD_evt!R36, "")</f>
-        <v>1</v>
-      </c>
-      <c r="XFD36" s="0"/>
+      <c r="I36" s="3" t="str">
+        <f aca="false">ADD_evt!P36</f>
+        <v>1</v>
+      </c>
+      <c r="J36" s="3" t="str">
+        <f aca="false">ADD_evt!Q36</f>
+        <v>0</v>
+      </c>
+      <c r="K36" s="21" t="n">
+        <f aca="false">ADD_evt!R36</f>
+        <v>1</v>
+      </c>
+      <c r="L36" s="3" t="str">
+        <f aca="false">ADD_vgp!P36</f>
+        <v>1</v>
+      </c>
+      <c r="M36" s="3" t="str">
+        <f aca="false">ADD_vgp!Q36</f>
+        <v>0</v>
+      </c>
+      <c r="N36" s="21" t="n">
+        <f aca="false">ADD_vgp!R36</f>
+        <v>1</v>
+      </c>
+      <c r="O36" s="10" t="n">
+        <f aca="false">IF(K36=N36,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P36" s="1" t="n">
+        <f aca="false">IF(O36=1,N(N36),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R36" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P36), ISERROR(Q36), P36="NA", Q36="NA"),
+   "NA",
+   N(P36) + N(Q36)
+)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="37" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="10" t="n">
@@ -14370,19 +15328,46 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3750869481267,2.13075902951078","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I37" s="10" t="n">
-        <f aca="false">IF(ADD_evt!R37=ADD_vgp!R37,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J37" s="21" t="b">
-        <f aca="false">IF(I37=1, ADD_evt!R37, "")</f>
-        <v>0</v>
-      </c>
-      <c r="K37" s="21" t="b">
-        <f aca="false">IF(I37=1, ADD_evt!R37, "")</f>
-        <v>0</v>
-      </c>
-      <c r="XFD37" s="0"/>
+      <c r="I37" s="3" t="str">
+        <f aca="false">ADD_evt!P37</f>
+        <v>0</v>
+      </c>
+      <c r="J37" s="3" t="str">
+        <f aca="false">ADD_evt!Q37</f>
+        <v>0</v>
+      </c>
+      <c r="K37" s="21" t="n">
+        <f aca="false">ADD_evt!R37</f>
+        <v>0</v>
+      </c>
+      <c r="L37" s="3" t="str">
+        <f aca="false">ADD_vgp!P37</f>
+        <v>1</v>
+      </c>
+      <c r="M37" s="3" t="str">
+        <f aca="false">ADD_vgp!Q37</f>
+        <v>1</v>
+      </c>
+      <c r="N37" s="21" t="n">
+        <f aca="false">ADD_vgp!R37</f>
+        <v>0</v>
+      </c>
+      <c r="O37" s="10" t="n">
+        <f aca="false">IF(K37=N37,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P37" s="1" t="n">
+        <f aca="false">IF(O37=1,N(N37),"")</f>
+        <v>0</v>
+      </c>
+      <c r="R37" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P37), ISERROR(Q37), P37="NA", Q37="NA"),
+   "NA",
+   N(P37) + N(Q37)
+)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="38" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="10" t="n">
@@ -14411,19 +15396,46 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3738399462803,2.13118777902404","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I38" s="10" t="n">
-        <f aca="false">IF(ADD_evt!R38=ADD_vgp!R38,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J38" s="21" t="b">
-        <f aca="false">IF(I38=1, ADD_evt!R38, "")</f>
-        <v>0</v>
-      </c>
-      <c r="K38" s="21" t="b">
-        <f aca="false">IF(I38=1, ADD_evt!R38, "")</f>
-        <v>0</v>
-      </c>
-      <c r="XFD38" s="0"/>
+      <c r="I38" s="3" t="str">
+        <f aca="false">ADD_evt!P38</f>
+        <v>0</v>
+      </c>
+      <c r="J38" s="3" t="str">
+        <f aca="false">ADD_evt!Q38</f>
+        <v>0</v>
+      </c>
+      <c r="K38" s="21" t="n">
+        <f aca="false">ADD_evt!R38</f>
+        <v>0</v>
+      </c>
+      <c r="L38" s="3" t="str">
+        <f aca="false">ADD_vgp!P38</f>
+        <v>1</v>
+      </c>
+      <c r="M38" s="3" t="str">
+        <f aca="false">ADD_vgp!Q38</f>
+        <v>1</v>
+      </c>
+      <c r="N38" s="21" t="n">
+        <f aca="false">ADD_vgp!R38</f>
+        <v>0</v>
+      </c>
+      <c r="O38" s="10" t="n">
+        <f aca="false">IF(K38=N38,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P38" s="1" t="n">
+        <f aca="false">IF(O38=1,N(N38),"")</f>
+        <v>0</v>
+      </c>
+      <c r="R38" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P38), ISERROR(Q38), P38="NA", Q38="NA"),
+   "NA",
+   N(P38) + N(Q38)
+)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="39" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="10" t="n">
@@ -14452,21 +15464,52 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4118804921771,2.17976081270431","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I39" s="10" t="n">
-        <f aca="false">IF(ADD_evt!R39=ADD_vgp!R39,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="J39" s="1" t="str">
-        <f aca="false">IF(I39=1, ADD_evt!R39, "")</f>
+      <c r="I39" s="3" t="str">
+        <f aca="false">ADD_evt!P39</f>
+        <v>1</v>
+      </c>
+      <c r="J39" s="3" t="str">
+        <f aca="false">ADD_evt!Q39</f>
+        <v>0</v>
+      </c>
+      <c r="K39" s="21" t="n">
+        <f aca="false">ADD_evt!R39</f>
+        <v>1</v>
+      </c>
+      <c r="L39" s="3" t="str">
+        <f aca="false">ADD_vgp!P39</f>
+        <v>0</v>
+      </c>
+      <c r="M39" s="3" t="str">
+        <f aca="false">ADD_vgp!Q39</f>
+        <v>0</v>
+      </c>
+      <c r="N39" s="21" t="n">
+        <f aca="false">ADD_vgp!R39</f>
+        <v>0</v>
+      </c>
+      <c r="O39" s="10" t="n">
+        <f aca="false">IF(K39=N39,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="P39" s="1" t="str">
+        <f aca="false">IF(O39=1,N(N39),"")</f>
         <v/>
       </c>
-      <c r="K39" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L39" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="XFD39" s="0"/>
+      <c r="Q39" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R39" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P39), ISERROR(Q39), P39="NA", Q39="NA"),
+   "NA",
+   N(P39) + N(Q39)
+)</f>
+        <v>1</v>
+      </c>
+      <c r="S39" s="1" t="s">
+        <v>259</v>
+      </c>
     </row>
     <row r="40" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="10" t="n">
@@ -14495,19 +15538,46 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4127447371871,2.180890772398","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I40" s="10" t="n">
-        <f aca="false">IF(ADD_evt!R40=ADD_vgp!R40,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J40" s="21" t="b">
-        <f aca="false">IF(I40=1, ADD_evt!R40, "")</f>
-        <v>0</v>
-      </c>
-      <c r="K40" s="21" t="b">
-        <f aca="false">IF(I40=1, ADD_evt!R40, "")</f>
-        <v>0</v>
-      </c>
-      <c r="XFD40" s="0"/>
+      <c r="I40" s="3" t="str">
+        <f aca="false">ADD_evt!P40</f>
+        <v>0</v>
+      </c>
+      <c r="J40" s="3" t="str">
+        <f aca="false">ADD_evt!Q40</f>
+        <v>0</v>
+      </c>
+      <c r="K40" s="21" t="n">
+        <f aca="false">ADD_evt!R40</f>
+        <v>0</v>
+      </c>
+      <c r="L40" s="3" t="str">
+        <f aca="false">ADD_vgp!P40</f>
+        <v>0</v>
+      </c>
+      <c r="M40" s="3" t="str">
+        <f aca="false">ADD_vgp!Q40</f>
+        <v>0</v>
+      </c>
+      <c r="N40" s="21" t="n">
+        <f aca="false">ADD_vgp!R40</f>
+        <v>0</v>
+      </c>
+      <c r="O40" s="10" t="n">
+        <f aca="false">IF(K40=N40,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P40" s="1" t="n">
+        <f aca="false">IF(O40=1,N(N40),"")</f>
+        <v>0</v>
+      </c>
+      <c r="R40" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P40), ISERROR(Q40), P40="NA", Q40="NA"),
+   "NA",
+   N(P40) + N(Q40)
+)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="41" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="10" t="n">
@@ -14536,19 +15606,46 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3848229909854,2.13736483373658","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I41" s="10" t="n">
-        <f aca="false">IF(ADD_evt!R41=ADD_vgp!R41,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J41" s="21" t="b">
-        <f aca="false">IF(I41=1, ADD_evt!R41, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K41" s="21" t="b">
-        <f aca="false">IF(I41=1, ADD_evt!R41, "")</f>
-        <v>1</v>
-      </c>
-      <c r="XFD41" s="0"/>
+      <c r="I41" s="3" t="str">
+        <f aca="false">ADD_evt!P41</f>
+        <v>1</v>
+      </c>
+      <c r="J41" s="3" t="str">
+        <f aca="false">ADD_evt!Q41</f>
+        <v>0</v>
+      </c>
+      <c r="K41" s="21" t="n">
+        <f aca="false">ADD_evt!R41</f>
+        <v>1</v>
+      </c>
+      <c r="L41" s="3" t="str">
+        <f aca="false">ADD_vgp!P41</f>
+        <v>1</v>
+      </c>
+      <c r="M41" s="3" t="str">
+        <f aca="false">ADD_vgp!Q41</f>
+        <v>0</v>
+      </c>
+      <c r="N41" s="21" t="n">
+        <f aca="false">ADD_vgp!R41</f>
+        <v>1</v>
+      </c>
+      <c r="O41" s="10" t="n">
+        <f aca="false">IF(K41=N41,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P41" s="1" t="n">
+        <f aca="false">IF(O41=1,N(N41),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R41" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P41), ISERROR(Q41), P41="NA", Q41="NA"),
+   "NA",
+   N(P41) + N(Q41)
+)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="42" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="10" t="n">
@@ -14577,19 +15674,46 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3851659046238,2.13784099621788","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I42" s="10" t="n">
-        <f aca="false">IF(ADD_evt!R42=ADD_vgp!R42,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J42" s="21" t="b">
-        <f aca="false">IF(I42=1, ADD_evt!R42, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K42" s="21" t="b">
-        <f aca="false">IF(I42=1, ADD_evt!R42, "")</f>
-        <v>1</v>
-      </c>
-      <c r="XFD42" s="0"/>
+      <c r="I42" s="3" t="str">
+        <f aca="false">ADD_evt!P42</f>
+        <v>1</v>
+      </c>
+      <c r="J42" s="3" t="str">
+        <f aca="false">ADD_evt!Q42</f>
+        <v>0</v>
+      </c>
+      <c r="K42" s="21" t="n">
+        <f aca="false">ADD_evt!R42</f>
+        <v>1</v>
+      </c>
+      <c r="L42" s="3" t="str">
+        <f aca="false">ADD_vgp!P42</f>
+        <v>1</v>
+      </c>
+      <c r="M42" s="3" t="str">
+        <f aca="false">ADD_vgp!Q42</f>
+        <v>0</v>
+      </c>
+      <c r="N42" s="21" t="n">
+        <f aca="false">ADD_vgp!R42</f>
+        <v>1</v>
+      </c>
+      <c r="O42" s="10" t="n">
+        <f aca="false">IF(K42=N42,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P42" s="1" t="n">
+        <f aca="false">IF(O42=1,N(N42),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R42" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P42), ISERROR(Q42), P42="NA", Q42="NA"),
+   "NA",
+   N(P42) + N(Q42)
+)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="43" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="10" t="n">
@@ -14618,19 +15742,46 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4166187121365,2.1905776282886","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I43" s="10" t="n">
-        <f aca="false">IF(ADD_evt!R43=ADD_vgp!R43,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J43" s="21" t="b">
-        <f aca="false">IF(I43=1, ADD_evt!R43, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K43" s="21" t="b">
-        <f aca="false">IF(I43=1, ADD_evt!R43, "")</f>
-        <v>1</v>
-      </c>
-      <c r="XFD43" s="0"/>
+      <c r="I43" s="3" t="str">
+        <f aca="false">ADD_evt!P43</f>
+        <v>1</v>
+      </c>
+      <c r="J43" s="3" t="str">
+        <f aca="false">ADD_evt!Q43</f>
+        <v>0</v>
+      </c>
+      <c r="K43" s="21" t="n">
+        <f aca="false">ADD_evt!R43</f>
+        <v>1</v>
+      </c>
+      <c r="L43" s="3" t="str">
+        <f aca="false">ADD_vgp!P43</f>
+        <v>1</v>
+      </c>
+      <c r="M43" s="3" t="str">
+        <f aca="false">ADD_vgp!Q43</f>
+        <v>0</v>
+      </c>
+      <c r="N43" s="21" t="n">
+        <f aca="false">ADD_vgp!R43</f>
+        <v>1</v>
+      </c>
+      <c r="O43" s="10" t="n">
+        <f aca="false">IF(K43=N43,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P43" s="1" t="n">
+        <f aca="false">IF(O43=1,N(N43),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R43" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P43), ISERROR(Q43), P43="NA", Q43="NA"),
+   "NA",
+   N(P43) + N(Q43)
+)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="10" t="n">
@@ -14659,19 +15810,47 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3600114226599,2.1392576352892","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I44" s="10" t="n">
-        <f aca="false">IF(ADD_evt!R44=ADD_vgp!R44,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J44" s="21" t="b">
-        <f aca="false">IF(I44=1, ADD_evt!R44, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K44" s="21" t="b">
-        <f aca="false">IF(I44=1, ADD_evt!R44, "")</f>
-        <v>1</v>
-      </c>
-      <c r="L44" s="1"/>
+      <c r="I44" s="3" t="str">
+        <f aca="false">ADD_evt!P44</f>
+        <v>1</v>
+      </c>
+      <c r="J44" s="3" t="str">
+        <f aca="false">ADD_evt!Q44</f>
+        <v>0</v>
+      </c>
+      <c r="K44" s="21" t="n">
+        <f aca="false">ADD_evt!R44</f>
+        <v>1</v>
+      </c>
+      <c r="L44" s="3" t="str">
+        <f aca="false">ADD_vgp!P44</f>
+        <v>1</v>
+      </c>
+      <c r="M44" s="3" t="str">
+        <f aca="false">ADD_vgp!Q44</f>
+        <v>0</v>
+      </c>
+      <c r="N44" s="21" t="n">
+        <f aca="false">ADD_vgp!R44</f>
+        <v>1</v>
+      </c>
+      <c r="O44" s="10" t="n">
+        <f aca="false">IF(K44=N44,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P44" s="1" t="n">
+        <f aca="false">IF(O44=1,N(N44),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R44" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P44), ISERROR(Q44), P44="NA", Q44="NA"),
+   "NA",
+   N(P44) + N(Q44)
+)</f>
+        <v>1</v>
+      </c>
+      <c r="S44" s="1"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="10" t="n">
@@ -14700,16 +15879,44 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3826401063928,2.14988483545965","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I45" s="10" t="n">
-        <f aca="false">IF(ADD_evt!R45=ADD_vgp!R45,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J45" s="21" t="b">
-        <f aca="false">IF(I45=1, ADD_evt!R45, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K45" s="21" t="b">
-        <f aca="false">IF(I45=1, ADD_evt!R45, "")</f>
+      <c r="I45" s="3" t="str">
+        <f aca="false">ADD_evt!P45</f>
+        <v>1</v>
+      </c>
+      <c r="J45" s="3" t="str">
+        <f aca="false">ADD_evt!Q45</f>
+        <v>0</v>
+      </c>
+      <c r="K45" s="21" t="n">
+        <f aca="false">ADD_evt!R45</f>
+        <v>1</v>
+      </c>
+      <c r="L45" s="3" t="str">
+        <f aca="false">ADD_vgp!P45</f>
+        <v>1</v>
+      </c>
+      <c r="M45" s="3" t="str">
+        <f aca="false">ADD_vgp!Q45</f>
+        <v>0</v>
+      </c>
+      <c r="N45" s="21" t="n">
+        <f aca="false">ADD_vgp!R45</f>
+        <v>1</v>
+      </c>
+      <c r="O45" s="10" t="n">
+        <f aca="false">IF(K45=N45,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P45" s="1" t="n">
+        <f aca="false">IF(O45=1,N(N45),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R45" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P45), ISERROR(Q45), P45="NA", Q45="NA"),
+   "NA",
+   N(P45) + N(Q45)
+)</f>
         <v>1</v>
       </c>
     </row>
@@ -14740,16 +15947,44 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.381818495143,2.15114251227034","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I46" s="10" t="n">
-        <f aca="false">IF(ADD_evt!R46=ADD_vgp!R46,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J46" s="21" t="b">
-        <f aca="false">IF(I46=1, ADD_evt!R46, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K46" s="21" t="b">
-        <f aca="false">IF(I46=1, ADD_evt!R46, "")</f>
+      <c r="I46" s="3" t="str">
+        <f aca="false">ADD_evt!P46</f>
+        <v>1</v>
+      </c>
+      <c r="J46" s="3" t="str">
+        <f aca="false">ADD_evt!Q46</f>
+        <v>0</v>
+      </c>
+      <c r="K46" s="21" t="n">
+        <f aca="false">ADD_evt!R46</f>
+        <v>1</v>
+      </c>
+      <c r="L46" s="3" t="str">
+        <f aca="false">ADD_vgp!P46</f>
+        <v>1</v>
+      </c>
+      <c r="M46" s="3" t="str">
+        <f aca="false">ADD_vgp!Q46</f>
+        <v>0</v>
+      </c>
+      <c r="N46" s="21" t="n">
+        <f aca="false">ADD_vgp!R46</f>
+        <v>1</v>
+      </c>
+      <c r="O46" s="10" t="n">
+        <f aca="false">IF(K46=N46,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P46" s="1" t="n">
+        <f aca="false">IF(O46=1,N(N46),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R46" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P46), ISERROR(Q46), P46="NA", Q46="NA"),
+   "NA",
+   N(P46) + N(Q46)
+)</f>
         <v>1</v>
       </c>
     </row>
@@ -14780,20 +16015,46 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3817275823742,2.15108663385945","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I47" s="10" t="n">
-        <f aca="false">IF(ADD_evt!R47=ADD_vgp!R47,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J47" s="21" t="b">
-        <f aca="false">IF(I47=1, ADD_evt!R47, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K47" s="21" t="b">
-        <f aca="false">IF(I47=1, ADD_evt!R47, "")</f>
-        <v>1</v>
-      </c>
-      <c r="L47" s="0"/>
-      <c r="XFD47" s="0"/>
+      <c r="I47" s="3" t="str">
+        <f aca="false">ADD_evt!P47</f>
+        <v>1</v>
+      </c>
+      <c r="J47" s="3" t="str">
+        <f aca="false">ADD_evt!Q47</f>
+        <v>0</v>
+      </c>
+      <c r="K47" s="21" t="n">
+        <f aca="false">ADD_evt!R47</f>
+        <v>1</v>
+      </c>
+      <c r="L47" s="3" t="str">
+        <f aca="false">ADD_vgp!P47</f>
+        <v>1</v>
+      </c>
+      <c r="M47" s="3" t="str">
+        <f aca="false">ADD_vgp!Q47</f>
+        <v>0</v>
+      </c>
+      <c r="N47" s="21" t="n">
+        <f aca="false">ADD_vgp!R47</f>
+        <v>1</v>
+      </c>
+      <c r="O47" s="10" t="n">
+        <f aca="false">IF(K47=N47,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P47" s="1" t="n">
+        <f aca="false">IF(O47=1,N(N47),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R47" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P47), ISERROR(Q47), P47="NA", Q47="NA"),
+   "NA",
+   N(P47) + N(Q47)
+)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="48" s="10" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="10" t="n">
@@ -14822,21 +16083,52 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3781971000936,2.15362165090984","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I48" s="10" t="s">
+      <c r="I48" s="3" t="str">
+        <f aca="false">ADD_evt!P48</f>
+        <v>NA</v>
+      </c>
+      <c r="J48" s="3" t="str">
+        <f aca="false">ADD_evt!Q48</f>
+        <v>NA</v>
+      </c>
+      <c r="K48" s="21" t="e">
+        <f aca="false">ADD_evt!R48</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L48" s="3" t="str">
+        <f aca="false">ADD_vgp!P48</f>
+        <v>1</v>
+      </c>
+      <c r="M48" s="3" t="str">
+        <f aca="false">ADD_vgp!Q48</f>
+        <v>1</v>
+      </c>
+      <c r="N48" s="21" t="n">
+        <f aca="false">ADD_vgp!R48</f>
+        <v>0</v>
+      </c>
+      <c r="O48" s="10" t="e">
+        <f aca="false">IF(K48=N48,1,0)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P48" s="1" t="e">
+        <f aca="false">IF(O48=1,N(N48),"")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q48" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J48" s="1" t="str">
-        <f aca="false">IF(I48=1, ADD_evt!R48, "")</f>
-        <v/>
-      </c>
-      <c r="K48" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="L48" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="XFC48" s="1"/>
-      <c r="XFD48" s="0"/>
+      <c r="R48" s="1" t="e">
+        <f aca="false">IF(
+   OR(ISERROR(P48), ISERROR(Q48), P48="NA", Q48="NA"),
+   "NA",
+   N(P48) + N(Q48)
+)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S48" s="10" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="49" s="10" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="10" t="n">
@@ -14865,22 +16157,52 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3826129597012,2.14763895462665","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I49" s="10" t="n">
-        <f aca="false">IF(ADD_evt!R49=ADD_vgp!R49,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="J49" s="1" t="str">
-        <f aca="false">IF(I49=1, ADD_evt!R49, "")</f>
+      <c r="I49" s="3" t="str">
+        <f aca="false">ADD_evt!P49</f>
+        <v>1</v>
+      </c>
+      <c r="J49" s="3" t="str">
+        <f aca="false">ADD_evt!Q49</f>
+        <v>0</v>
+      </c>
+      <c r="K49" s="21" t="n">
+        <f aca="false">ADD_evt!R49</f>
+        <v>1</v>
+      </c>
+      <c r="L49" s="3" t="str">
+        <f aca="false">ADD_vgp!P49</f>
+        <v>0</v>
+      </c>
+      <c r="M49" s="3" t="str">
+        <f aca="false">ADD_vgp!Q49</f>
+        <v>0</v>
+      </c>
+      <c r="N49" s="21" t="n">
+        <f aca="false">ADD_vgp!R49</f>
+        <v>0</v>
+      </c>
+      <c r="O49" s="10" t="n">
+        <f aca="false">IF(K49=N49,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="P49" s="1" t="str">
+        <f aca="false">IF(O49=1,N(N49),"")</f>
         <v/>
       </c>
-      <c r="K49" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L49" s="10" t="s">
-        <v>253</v>
-      </c>
-      <c r="XFC49" s="1"/>
-      <c r="XFD49" s="0"/>
+      <c r="Q49" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R49" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P49), ISERROR(Q49), P49="NA", Q49="NA"),
+   "NA",
+   N(P49) + N(Q49)
+)</f>
+        <v>1</v>
+      </c>
+      <c r="S49" s="10" t="s">
+        <v>260</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="10" t="n">
@@ -14909,52 +16231,75 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3830424246768,2.14820775338395","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I50" s="10" t="n">
-        <f aca="false">IF(ADD_evt!R50=ADD_vgp!R50,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="J50" s="1" t="str">
-        <f aca="false">IF(I50=1, ADD_evt!R50, "")</f>
+      <c r="I50" s="3" t="str">
+        <f aca="false">ADD_evt!P50</f>
+        <v>1</v>
+      </c>
+      <c r="J50" s="3" t="str">
+        <f aca="false">ADD_evt!Q50</f>
+        <v>0</v>
+      </c>
+      <c r="K50" s="21" t="n">
+        <f aca="false">ADD_evt!R50</f>
+        <v>1</v>
+      </c>
+      <c r="L50" s="3" t="str">
+        <f aca="false">ADD_vgp!P50</f>
+        <v>0</v>
+      </c>
+      <c r="M50" s="3" t="str">
+        <f aca="false">ADD_vgp!Q50</f>
+        <v>0</v>
+      </c>
+      <c r="N50" s="21" t="n">
+        <f aca="false">ADD_vgp!R50</f>
+        <v>0</v>
+      </c>
+      <c r="O50" s="10" t="n">
+        <f aca="false">IF(K50=N50,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="P50" s="1" t="str">
+        <f aca="false">IF(O50=1,N(N50),"")</f>
         <v/>
       </c>
-      <c r="K50" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" s="10" t="s">
-        <v>254</v>
+      <c r="Q50" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P50), ISERROR(Q50), P50="NA", Q50="NA"),
+   "NA",
+   N(P50) + N(Q50)
+)</f>
+        <v>0</v>
+      </c>
+      <c r="S50" s="10" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I51" s="12" t="n">
-        <f aca="false">COUNTIFS(I3:I50,1)</f>
+      <c r="O51" s="12" t="n">
+        <f aca="false">COUNTIFS(O3:O50,1)</f>
         <v>41</v>
       </c>
-      <c r="J51" s="1" t="str">
-        <f aca="false">IF(I51=1, ADD_evt!R51, "")</f>
-        <v/>
-      </c>
-      <c r="K51" s="12" t="n">
-        <f aca="false">COUNTIFS(K3:K50,1)</f>
+      <c r="P51" s="12"/>
+      <c r="Q51" s="0"/>
+      <c r="R51" s="12" t="n">
+        <f aca="false">COUNTIFS(R3:R50,1)</f>
         <v>34</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I52" s="22" t="n">
-        <f aca="false">COUNTIFS(I3:I50,1) / (COUNTIFS(I3:I50,1) + COUNTIFS(I3:I50,0))</f>
+      <c r="O52" s="22" t="n">
+        <f aca="false">COUNTIFS(O3:O50,1) / (COUNTIFS(O3:O50,1) + COUNTIFS(O3:O50,0))</f>
         <v>0.931818181818182</v>
       </c>
-      <c r="J52" s="22"/>
-      <c r="K52" s="23" t="n">
-        <f aca="false">COUNTIFS(K3:K50,1) / (COUNTIFS(K3:K50,1) + COUNTIFS(K3:K50,0))</f>
+      <c r="P52" s="22"/>
+      <c r="Q52" s="0"/>
+      <c r="R52" s="23" t="n">
+        <f aca="false">COUNTIFS(R3:R50,1) / (COUNTIFS(R3:R50,1) + COUNTIFS(R3:R50,0))</f>
         <v>0.772727272727273</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I53" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="K53" s="1" t="s">
-        <v>256</v>
       </c>
     </row>
   </sheetData>
@@ -14973,45 +16318,23 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:XFC13"/>
+  <dimension ref="A1:X13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="9.08"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="8.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="3.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="3.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="15.62"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="4" min="4" style="1" width="8.24"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="5" min="5" style="1" width="3.89"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="6" min="6" style="1" width="3.61"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="7" min="7" style="1" width="15.62"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="12.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="15.62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="12.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="13.81"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16383" min="16382" style="0" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="9" style="1" width="15.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="12.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="17" style="1" width="13.81"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0"/>
-      <c r="B1" s="0"/>
-      <c r="C1" s="0"/>
-      <c r="D1" s="0"/>
-      <c r="E1" s="0"/>
-      <c r="F1" s="0"/>
-      <c r="G1" s="0"/>
-      <c r="H1" s="0"/>
-      <c r="I1" s="0"/>
-      <c r="J1" s="0"/>
-      <c r="K1" s="0"/>
-      <c r="L1" s="0"/>
-      <c r="M1" s="0"/>
-      <c r="N1" s="0"/>
-      <c r="O1" s="0"/>
-      <c r="P1" s="0"/>
-      <c r="Q1" s="0"/>
-      <c r="XFB1" s="0"/>
-      <c r="XFC1" s="0"/>
-    </row>
+    <row r="1" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="2" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="20" t="s">
         <v>2</v>
@@ -15037,17 +16360,36 @@
       <c r="H2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="20" t="s">
+      <c r="I2" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="J2" s="20" t="s">
+      <c r="J2" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="K2" s="20" t="s">
+      <c r="K2" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="XFB2" s="0"/>
-      <c r="XFC2" s="0"/>
+      <c r="L2" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="O2" s="20" t="s">
+        <v>254</v>
+      </c>
+      <c r="P2" s="20" t="s">
+        <v>255</v>
+      </c>
+      <c r="Q2" s="20" t="s">
+        <v>256</v>
+      </c>
+      <c r="R2" s="20" t="s">
+        <v>257</v>
+      </c>
     </row>
     <row r="3" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="n">
@@ -15076,20 +16418,47 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3849403989724,2.10400617396064","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I3" s="10" t="n">
-        <f aca="false">IF(REMOVE_evt!R3=REMOVE_vgp!R3,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J3" s="21" t="n">
-        <f aca="false">IF(I3=1, REMOVE_evt!R3, "")</f>
-        <v>0</v>
-      </c>
-      <c r="K3" s="21" t="n">
-        <f aca="false">IF(I3=1, REMOVE_evt!R3, "")</f>
-        <v>0</v>
-      </c>
-      <c r="XFB3" s="0"/>
-      <c r="XFC3" s="0"/>
+      <c r="I3" s="3" t="str">
+        <f aca="false">REMOVE_evt!P3</f>
+        <v>0</v>
+      </c>
+      <c r="J3" s="3" t="str">
+        <f aca="false">REMOVE_evt!Q3</f>
+        <v>0</v>
+      </c>
+      <c r="K3" s="21" t="b">
+        <f aca="false">REMOVE_evt!R3</f>
+        <v>0</v>
+      </c>
+      <c r="L3" s="3" t="str">
+        <f aca="false">REMOVE_vgp!P3</f>
+        <v>0</v>
+      </c>
+      <c r="M3" s="3" t="str">
+        <f aca="false">REMOVE_vgp!Q3</f>
+        <v>0</v>
+      </c>
+      <c r="N3" s="21" t="b">
+        <f aca="false">REMOVE_vgp!R3</f>
+        <v>0</v>
+      </c>
+      <c r="O3" s="10" t="n">
+        <f aca="false">IF(K3=N3,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P3" s="1" t="n">
+        <f aca="false">IF(O3=1, N(N3), "")</f>
+        <v>0</v>
+      </c>
+      <c r="Q3" s="24"/>
+      <c r="R3" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P3), ISERROR(Q3), P3="NA", Q3="NA"),
+   "NA",
+   N(P3) + N(Q3)
+)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="4" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="n">
@@ -15118,20 +16487,47 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4201900660698,2.20077984083242","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I4" s="10" t="n">
-        <f aca="false">IF(REMOVE_evt!R4=REMOVE_vgp!R4,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J4" s="1" t="n">
-        <f aca="false">IF(I4=1, REMOVE_evt!R4, "")</f>
-        <v>0</v>
-      </c>
-      <c r="K4" s="1" t="n">
-        <f aca="false">IF(I4=1, REMOVE_evt!R4, "")</f>
-        <v>0</v>
-      </c>
-      <c r="XFB4" s="0"/>
-      <c r="XFC4" s="0"/>
+      <c r="I4" s="3" t="str">
+        <f aca="false">REMOVE_evt!P4</f>
+        <v>1</v>
+      </c>
+      <c r="J4" s="3" t="str">
+        <f aca="false">REMOVE_evt!Q4</f>
+        <v>1</v>
+      </c>
+      <c r="K4" s="21" t="n">
+        <f aca="false">REMOVE_evt!R4</f>
+        <v>0</v>
+      </c>
+      <c r="L4" s="3" t="str">
+        <f aca="false">REMOVE_vgp!P4</f>
+        <v>1</v>
+      </c>
+      <c r="M4" s="3" t="str">
+        <f aca="false">REMOVE_vgp!Q4</f>
+        <v>1</v>
+      </c>
+      <c r="N4" s="21" t="n">
+        <f aca="false">REMOVE_vgp!R4</f>
+        <v>0</v>
+      </c>
+      <c r="O4" s="10" t="n">
+        <f aca="false">IF(K4=N4,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P4" s="1" t="n">
+        <f aca="false">IF(O4=1, N(N4), "")</f>
+        <v>0</v>
+      </c>
+      <c r="Q4" s="24"/>
+      <c r="R4" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P4), ISERROR(Q4), P4="NA", Q4="NA"),
+   "NA",
+   N(P4) + N(Q4)
+)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="5" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="n">
@@ -15160,20 +16556,47 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3753719135312,2.14838582462673","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I5" s="10" t="n">
-        <f aca="false">IF(REMOVE_evt!R5=REMOVE_vgp!R5,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J5" s="1" t="n">
-        <f aca="false">IF(I5=1, REMOVE_evt!R5, "")</f>
-        <v>0</v>
-      </c>
-      <c r="K5" s="1" t="n">
-        <f aca="false">IF(I5=1, REMOVE_evt!R5, "")</f>
-        <v>0</v>
-      </c>
-      <c r="XFB5" s="0"/>
-      <c r="XFC5" s="0"/>
+      <c r="I5" s="3" t="str">
+        <f aca="false">REMOVE_evt!P5</f>
+        <v>0</v>
+      </c>
+      <c r="J5" s="3" t="str">
+        <f aca="false">REMOVE_evt!Q5</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="21" t="n">
+        <f aca="false">REMOVE_evt!R5</f>
+        <v>0</v>
+      </c>
+      <c r="L5" s="3" t="str">
+        <f aca="false">REMOVE_vgp!P5</f>
+        <v>0</v>
+      </c>
+      <c r="M5" s="3" t="str">
+        <f aca="false">REMOVE_vgp!Q5</f>
+        <v>0</v>
+      </c>
+      <c r="N5" s="21" t="n">
+        <f aca="false">REMOVE_vgp!R5</f>
+        <v>0</v>
+      </c>
+      <c r="O5" s="10" t="n">
+        <f aca="false">IF(K5=N5,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P5" s="1" t="n">
+        <f aca="false">IF(O5=1, N(N5), "")</f>
+        <v>0</v>
+      </c>
+      <c r="Q5" s="24"/>
+      <c r="R5" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P5), ISERROR(Q5), P5="NA", Q5="NA"),
+   "NA",
+   N(P5) + N(Q5)
+)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="6" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="n">
@@ -15202,20 +16625,47 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4325734990105,2.17979187635586","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I6" s="10" t="n">
-        <f aca="false">IF(REMOVE_evt!R6=REMOVE_vgp!R6,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J6" s="1" t="n">
-        <f aca="false">IF(I6=1, REMOVE_evt!R6, "")</f>
-        <v>0</v>
-      </c>
-      <c r="K6" s="1" t="n">
-        <f aca="false">IF(I6=1, REMOVE_evt!R6, "")</f>
-        <v>0</v>
-      </c>
-      <c r="XFB6" s="0"/>
-      <c r="XFC6" s="0"/>
+      <c r="I6" s="3" t="str">
+        <f aca="false">REMOVE_evt!P6</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="str">
+        <f aca="false">REMOVE_evt!Q6</f>
+        <v>0</v>
+      </c>
+      <c r="K6" s="21" t="n">
+        <f aca="false">REMOVE_evt!R6</f>
+        <v>0</v>
+      </c>
+      <c r="L6" s="3" t="str">
+        <f aca="false">REMOVE_vgp!P6</f>
+        <v>0</v>
+      </c>
+      <c r="M6" s="3" t="str">
+        <f aca="false">REMOVE_vgp!Q6</f>
+        <v>0</v>
+      </c>
+      <c r="N6" s="21" t="n">
+        <f aca="false">REMOVE_vgp!R6</f>
+        <v>0</v>
+      </c>
+      <c r="O6" s="10" t="n">
+        <f aca="false">IF(K6=N6,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P6" s="1" t="n">
+        <f aca="false">IF(O6=1, N(N6), "")</f>
+        <v>0</v>
+      </c>
+      <c r="Q6" s="24"/>
+      <c r="R6" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P6), ISERROR(Q6), P6="NA", Q6="NA"),
+   "NA",
+   N(P6) + N(Q6)
+)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="7" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="n">
@@ -15244,20 +16694,47 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4302401188698,2.17443553665477","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I7" s="10" t="n">
-        <f aca="false">IF(REMOVE_evt!R7=REMOVE_vgp!R7,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J7" s="1" t="n">
-        <f aca="false">IF(I7=1, REMOVE_evt!R7, "")</f>
-        <v>0</v>
-      </c>
-      <c r="K7" s="1" t="n">
-        <f aca="false">IF(I7=1, REMOVE_evt!R7, "")</f>
-        <v>0</v>
-      </c>
-      <c r="XFB7" s="0"/>
-      <c r="XFC7" s="0"/>
+      <c r="I7" s="3" t="str">
+        <f aca="false">REMOVE_evt!P7</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="str">
+        <f aca="false">REMOVE_evt!Q7</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="21" t="n">
+        <f aca="false">REMOVE_evt!R7</f>
+        <v>0</v>
+      </c>
+      <c r="L7" s="3" t="str">
+        <f aca="false">REMOVE_vgp!P7</f>
+        <v>1</v>
+      </c>
+      <c r="M7" s="3" t="str">
+        <f aca="false">REMOVE_vgp!Q7</f>
+        <v>1</v>
+      </c>
+      <c r="N7" s="21" t="n">
+        <f aca="false">REMOVE_vgp!R7</f>
+        <v>0</v>
+      </c>
+      <c r="O7" s="10" t="n">
+        <f aca="false">IF(K7=N7,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P7" s="1" t="n">
+        <f aca="false">IF(O7=1, N(N7), "")</f>
+        <v>0</v>
+      </c>
+      <c r="Q7" s="24"/>
+      <c r="R7" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P7), ISERROR(Q7), P7="NA", Q7="NA"),
+   "NA",
+   N(P7) + N(Q7)
+)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="8" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="n">
@@ -15286,20 +16763,47 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3843400360326,2.15681272246317","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I8" s="10" t="n">
-        <f aca="false">IF(REMOVE_evt!R8=REMOVE_vgp!R8,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J8" s="1" t="n">
-        <f aca="false">IF(I8=1, REMOVE_evt!R8, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K8" s="1" t="n">
-        <f aca="false">IF(I8=1, REMOVE_evt!R8, "")</f>
-        <v>1</v>
-      </c>
-      <c r="XFB8" s="0"/>
-      <c r="XFC8" s="0"/>
+      <c r="I8" s="3" t="str">
+        <f aca="false">REMOVE_evt!P8</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="str">
+        <f aca="false">REMOVE_evt!Q8</f>
+        <v>1</v>
+      </c>
+      <c r="K8" s="21" t="n">
+        <f aca="false">REMOVE_evt!R8</f>
+        <v>1</v>
+      </c>
+      <c r="L8" s="3" t="str">
+        <f aca="false">REMOVE_vgp!P8</f>
+        <v>0</v>
+      </c>
+      <c r="M8" s="3" t="str">
+        <f aca="false">REMOVE_vgp!Q8</f>
+        <v>1</v>
+      </c>
+      <c r="N8" s="21" t="n">
+        <f aca="false">REMOVE_vgp!R8</f>
+        <v>1</v>
+      </c>
+      <c r="O8" s="10" t="n">
+        <f aca="false">IF(K8=N8,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P8" s="1" t="n">
+        <f aca="false">IF(O8=1, N(N8), "")</f>
+        <v>1</v>
+      </c>
+      <c r="Q8" s="24"/>
+      <c r="R8" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P8), ISERROR(Q8), P8="NA", Q8="NA"),
+   "NA",
+   N(P8) + N(Q8)
+)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="9" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="n">
@@ -15328,21 +16832,50 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3832798659396,2.15726201275132","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I9" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J9" s="1" t="str">
-        <f aca="false">IF(I9=1, REMOVE_evt!R9, "")</f>
-        <v/>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="L9" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="XFB9" s="0"/>
-      <c r="XFC9" s="0"/>
+      <c r="I9" s="3" t="str">
+        <f aca="false">REMOVE_evt!P9</f>
+        <v>NA</v>
+      </c>
+      <c r="J9" s="3" t="str">
+        <f aca="false">REMOVE_evt!Q9</f>
+        <v>NA</v>
+      </c>
+      <c r="K9" s="21" t="e">
+        <f aca="false">REMOVE_evt!R9</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L9" s="3" t="str">
+        <f aca="false">REMOVE_vgp!P9</f>
+        <v>0</v>
+      </c>
+      <c r="M9" s="3" t="str">
+        <f aca="false">REMOVE_vgp!Q9</f>
+        <v>1</v>
+      </c>
+      <c r="N9" s="21" t="n">
+        <f aca="false">REMOVE_vgp!R9</f>
+        <v>1</v>
+      </c>
+      <c r="O9" s="10" t="e">
+        <f aca="false">IF(K9=N9,1,0)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P9" s="1" t="e">
+        <f aca="false">IF(O9=1, N(N9), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q9" s="24"/>
+      <c r="R9" s="1" t="e">
+        <f aca="false">IF(
+   OR(ISERROR(P9), ISERROR(Q9), P9="NA", Q9="NA"),
+   "NA",
+   N(P9) + N(Q9)
+)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S9" s="10" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="10" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="n">
@@ -15371,20 +16904,47 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3809395290626,2.15213844443264","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I10" s="10" t="n">
-        <f aca="false">IF(REMOVE_evt!R10=REMOVE_vgp!R10,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J10" s="1" t="n">
-        <f aca="false">IF(I10=1, REMOVE_evt!R10, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K10" s="21" t="b">
-        <f aca="false">IF(I10=1, REMOVE_evt!R10, "")</f>
-        <v>1</v>
-      </c>
-      <c r="XFB10" s="0"/>
-      <c r="XFC10" s="0"/>
+      <c r="I10" s="3" t="str">
+        <f aca="false">REMOVE_evt!P10</f>
+        <v>0</v>
+      </c>
+      <c r="J10" s="3" t="str">
+        <f aca="false">REMOVE_evt!Q10</f>
+        <v>1</v>
+      </c>
+      <c r="K10" s="21" t="n">
+        <f aca="false">REMOVE_evt!R10</f>
+        <v>1</v>
+      </c>
+      <c r="L10" s="3" t="str">
+        <f aca="false">REMOVE_vgp!P10</f>
+        <v>0</v>
+      </c>
+      <c r="M10" s="3" t="str">
+        <f aca="false">REMOVE_vgp!Q10</f>
+        <v>1</v>
+      </c>
+      <c r="N10" s="21" t="n">
+        <f aca="false">REMOVE_vgp!R10</f>
+        <v>1</v>
+      </c>
+      <c r="O10" s="10" t="n">
+        <f aca="false">IF(K10=N10,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P10" s="1" t="n">
+        <f aca="false">IF(O10=1, N(N10), "")</f>
+        <v>1</v>
+      </c>
+      <c r="Q10" s="24"/>
+      <c r="R10" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P10), ISERROR(Q10), P10="NA", Q10="NA"),
+   "NA",
+   N(P10) + N(Q10)
+)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="11" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10"/>
@@ -15395,20 +16955,24 @@
       <c r="F11" s="10"/>
       <c r="G11" s="10"/>
       <c r="H11" s="10"/>
-      <c r="I11" s="12" t="n">
-        <f aca="false">COUNTIFS(I3:I10,1)</f>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="10"/>
+      <c r="O11" s="12" t="n">
+        <f aca="false">COUNTIFS(O3:O10,1)</f>
         <v>7</v>
       </c>
-      <c r="J11" s="1" t="str">
-        <f aca="false">IF(I11=1, ADD_evt!R11, "")</f>
+      <c r="P11" s="1" t="str">
+        <f aca="false">IF(O11=1, ADD_evt!R11, "")</f>
         <v/>
       </c>
-      <c r="K11" s="12" t="n">
-        <f aca="false">COUNTIFS(K3:K10,1)</f>
+      <c r="R11" s="12" t="n">
+        <f aca="false">COUNTIFS(R3:R10,1)</f>
         <v>2</v>
       </c>
-      <c r="XFB11" s="0"/>
-      <c r="XFC11" s="0"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10"/>
@@ -15419,21 +16983,28 @@
       <c r="F12" s="10"/>
       <c r="G12" s="10"/>
       <c r="H12" s="10"/>
-      <c r="I12" s="22" t="n">
-        <f aca="false">COUNTIFS(I3:I10,1) / (COUNTIFS(I3:I10,1) + COUNTIFS(I3:I10,0))</f>
-        <v>1</v>
-      </c>
-      <c r="J12" s="22"/>
-      <c r="K12" s="23" t="n">
-        <f aca="false">COUNTIFS(K3:K10,1) / (COUNTIFS(K3:K10,1) + COUNTIFS(K3:K10,0))</f>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="10"/>
+      <c r="N12" s="10"/>
+      <c r="O12" s="22" t="n">
+        <f aca="false">COUNTIFS(O3:O10,1) / (COUNTIFS(O3:O10,1) + COUNTIFS(O3:O10,0))</f>
+        <v>1</v>
+      </c>
+      <c r="P12" s="22"/>
+      <c r="Q12" s="22"/>
+      <c r="R12" s="23" t="n">
+        <f aca="false">COUNTIFS(R3:R10,1) / (COUNTIFS(R3:R10,1) + COUNTIFS(R3:R10,0))</f>
         <v>0.285714285714286</v>
       </c>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1"/>
-      <c r="P12" s="1"/>
-      <c r="Q12" s="1"/>
+      <c r="S12" s="1"/>
+      <c r="T12" s="1"/>
+      <c r="U12" s="1"/>
+      <c r="V12" s="1"/>
+      <c r="W12" s="1"/>
+      <c r="X12" s="1"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10"/>
@@ -15444,12 +17015,12 @@
       <c r="F13" s="10"/>
       <c r="G13" s="10"/>
       <c r="H13" s="10"/>
-      <c r="I13" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>256</v>
-      </c>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="10"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -15467,35 +17038,25 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L54"/>
+  <dimension ref="A1:S54"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.79"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="7.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="8.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="3.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="3.05"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="12.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="15.62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="12.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="13.81"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16382" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="4" min="4" style="1" width="8.24"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="5" min="5" style="1" width="3.34"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="6" min="6" style="1" width="3.05"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="7" min="7" style="1" width="12.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="12.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="9" style="1" width="15.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="12.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="12.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="13.81"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0"/>
-      <c r="B1" s="0"/>
-      <c r="C1" s="0"/>
-      <c r="D1" s="0"/>
-      <c r="E1" s="0"/>
-      <c r="F1" s="0"/>
-      <c r="G1" s="0"/>
-      <c r="H1" s="0"/>
-      <c r="I1" s="0"/>
-      <c r="J1" s="0"/>
-      <c r="K1" s="0"/>
-      <c r="L1" s="0"/>
+      <c r="Q1" s="0"/>
     </row>
     <row r="2" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="20" t="s">
@@ -15522,14 +17083,35 @@
       <c r="H2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="20" t="s">
+      <c r="I2" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="J2" s="20" t="s">
+      <c r="J2" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="K2" s="20" t="s">
+      <c r="K2" s="6" t="s">
         <v>250</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="O2" s="20" t="s">
+        <v>254</v>
+      </c>
+      <c r="P2" s="20" t="s">
+        <v>255</v>
+      </c>
+      <c r="Q2" s="20" t="s">
+        <v>256</v>
+      </c>
+      <c r="R2" s="20" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15559,15 +17141,45 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3895594523829,2.10441235059915","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I3" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J3" s="1" t="str">
-        <f aca="false">IF(I3=1, NONCI_evt!R3, "")</f>
-        <v/>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>24</v>
+      <c r="I3" s="3" t="str">
+        <f aca="false">NONCI_evt!P3</f>
+        <v>NA</v>
+      </c>
+      <c r="J3" s="3" t="str">
+        <f aca="false">NONCI_evt!Q3</f>
+        <v>NA</v>
+      </c>
+      <c r="K3" s="3" t="e">
+        <f aca="false">NONCI_evt!R3</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L3" s="3" t="str">
+        <f aca="false">NONCI_vgp!P3</f>
+        <v>NA</v>
+      </c>
+      <c r="M3" s="3" t="str">
+        <f aca="false">NONCI_vgp!Q3</f>
+        <v>NA</v>
+      </c>
+      <c r="N3" s="3" t="e">
+        <f aca="false">NONCI_vgp!R3</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O3" s="10" t="e">
+        <f aca="false">IF(K3=N3,1,0)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P3" s="1" t="e">
+        <f aca="false">IF(O3=1,N(N3),"")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R3" s="1" t="e">
+        <f aca="false">IF(
+   OR(ISERROR(P3), ISERROR(Q3), P3="NA", Q3="NA"),
+   "NA",
+   N(P3) + N(Q3)
+)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15597,16 +17209,44 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4216820407901,2.16919488937241","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I4" s="10" t="n">
-        <f aca="false">IF(NONCI_evt!R4=NONCI_vgp!R4,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J4" s="21" t="b">
-        <f aca="false">IF(I4=1, NONCI_evt!R4, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K4" s="21" t="b">
-        <f aca="false">IF(I4=1, NONCI_evt!R4, "")</f>
+      <c r="I4" s="3" t="str">
+        <f aca="false">NONCI_evt!P4</f>
+        <v>0</v>
+      </c>
+      <c r="J4" s="3" t="str">
+        <f aca="false">NONCI_evt!Q4</f>
+        <v>0</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <f aca="false">NONCI_evt!R4</f>
+        <v>1</v>
+      </c>
+      <c r="L4" s="3" t="str">
+        <f aca="false">NONCI_vgp!P4</f>
+        <v>0</v>
+      </c>
+      <c r="M4" s="3" t="str">
+        <f aca="false">NONCI_vgp!Q4</f>
+        <v>0</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <f aca="false">NONCI_vgp!R4</f>
+        <v>1</v>
+      </c>
+      <c r="O4" s="10" t="n">
+        <f aca="false">IF(K4=N4,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P4" s="1" t="n">
+        <f aca="false">IF(O4=1,N(N4),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R4" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P4), ISERROR(Q4), P4="NA", Q4="NA"),
+   "NA",
+   N(P4) + N(Q4)
+)</f>
         <v>1</v>
       </c>
     </row>
@@ -15637,15 +17277,45 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4549903058703,2.17916326903095","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I5" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5" s="1" t="str">
-        <f aca="false">IF(I5=1, NONCI_evt!R5, "")</f>
-        <v/>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>24</v>
+      <c r="I5" s="3" t="str">
+        <f aca="false">NONCI_evt!P5</f>
+        <v>NA</v>
+      </c>
+      <c r="J5" s="3" t="str">
+        <f aca="false">NONCI_evt!Q5</f>
+        <v>NA</v>
+      </c>
+      <c r="K5" s="3" t="e">
+        <f aca="false">NONCI_evt!R5</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L5" s="3" t="str">
+        <f aca="false">NONCI_vgp!P5</f>
+        <v>NA</v>
+      </c>
+      <c r="M5" s="3" t="str">
+        <f aca="false">NONCI_vgp!Q5</f>
+        <v>NA</v>
+      </c>
+      <c r="N5" s="3" t="e">
+        <f aca="false">NONCI_vgp!R5</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O5" s="10" t="e">
+        <f aca="false">IF(K5=N5,1,0)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P5" s="1" t="e">
+        <f aca="false">IF(O5=1,N(N5),"")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R5" s="1" t="e">
+        <f aca="false">IF(
+   OR(ISERROR(P5), ISERROR(Q5), P5="NA", Q5="NA"),
+   "NA",
+   N(P5) + N(Q5)
+)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15675,16 +17345,44 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4152785875993,2.13908529805925","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I6" s="10" t="n">
-        <f aca="false">IF(NONCI_evt!R6=NONCI_vgp!R6,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J6" s="21" t="b">
-        <f aca="false">IF(I6=1, NONCI_evt!R6, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K6" s="21" t="b">
-        <f aca="false">IF(I6=1, NONCI_evt!R6, "")</f>
+      <c r="I6" s="3" t="str">
+        <f aca="false">NONCI_evt!P6</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="str">
+        <f aca="false">NONCI_evt!Q6</f>
+        <v>0</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <f aca="false">NONCI_evt!R6</f>
+        <v>1</v>
+      </c>
+      <c r="L6" s="3" t="str">
+        <f aca="false">NONCI_vgp!P6</f>
+        <v>0</v>
+      </c>
+      <c r="M6" s="3" t="str">
+        <f aca="false">NONCI_vgp!Q6</f>
+        <v>0</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <f aca="false">NONCI_vgp!R6</f>
+        <v>1</v>
+      </c>
+      <c r="O6" s="10" t="n">
+        <f aca="false">IF(K6=N6,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P6" s="1" t="n">
+        <f aca="false">IF(O6=1,N(N6),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R6" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P6), ISERROR(Q6), P6="NA", Q6="NA"),
+   "NA",
+   N(P6) + N(Q6)
+)</f>
         <v>1</v>
       </c>
     </row>
@@ -15715,16 +17413,44 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4229756102428,2.20906860933044","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I7" s="10" t="n">
-        <f aca="false">IF(NONCI_evt!R7=NONCI_vgp!R7,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J7" s="21" t="b">
-        <f aca="false">IF(I7=1, NONCI_evt!R7, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K7" s="21" t="b">
-        <f aca="false">IF(I7=1, NONCI_evt!R7, "")</f>
+      <c r="I7" s="3" t="str">
+        <f aca="false">NONCI_evt!P7</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="str">
+        <f aca="false">NONCI_evt!Q7</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <f aca="false">NONCI_evt!R7</f>
+        <v>1</v>
+      </c>
+      <c r="L7" s="3" t="str">
+        <f aca="false">NONCI_vgp!P7</f>
+        <v>0</v>
+      </c>
+      <c r="M7" s="3" t="str">
+        <f aca="false">NONCI_vgp!Q7</f>
+        <v>0</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <f aca="false">NONCI_vgp!R7</f>
+        <v>1</v>
+      </c>
+      <c r="O7" s="10" t="n">
+        <f aca="false">IF(K7=N7,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P7" s="1" t="n">
+        <f aca="false">IF(O7=1,N(N7),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R7" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P7), ISERROR(Q7), P7="NA", Q7="NA"),
+   "NA",
+   N(P7) + N(Q7)
+)</f>
         <v>1</v>
       </c>
     </row>
@@ -15755,16 +17481,44 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4258905806347,2.20484681868868","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I8" s="10" t="n">
-        <f aca="false">IF(NONCI_evt!R8=NONCI_vgp!R8,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J8" s="21" t="b">
-        <f aca="false">IF(I8=1, NONCI_evt!R8, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K8" s="21" t="b">
-        <f aca="false">IF(I8=1, NONCI_evt!R8, "")</f>
+      <c r="I8" s="3" t="str">
+        <f aca="false">NONCI_evt!P8</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="str">
+        <f aca="false">NONCI_evt!Q8</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <f aca="false">NONCI_evt!R8</f>
+        <v>1</v>
+      </c>
+      <c r="L8" s="3" t="str">
+        <f aca="false">NONCI_vgp!P8</f>
+        <v>0</v>
+      </c>
+      <c r="M8" s="3" t="str">
+        <f aca="false">NONCI_vgp!Q8</f>
+        <v>0</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <f aca="false">NONCI_vgp!R8</f>
+        <v>1</v>
+      </c>
+      <c r="O8" s="10" t="n">
+        <f aca="false">IF(K8=N8,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P8" s="1" t="n">
+        <f aca="false">IF(O8=1,N(N8),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R8" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P8), ISERROR(Q8), P8="NA", Q8="NA"),
+   "NA",
+   N(P8) + N(Q8)
+)</f>
         <v>1</v>
       </c>
     </row>
@@ -15795,16 +17549,44 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3886459941181,2.13605268130468","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I9" s="10" t="n">
-        <f aca="false">IF(NONCI_evt!R9=NONCI_vgp!R9,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J9" s="21" t="b">
-        <f aca="false">IF(I9=1, NONCI_evt!R9, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K9" s="21" t="b">
-        <f aca="false">IF(I9=1, NONCI_evt!R9, "")</f>
+      <c r="I9" s="3" t="str">
+        <f aca="false">NONCI_evt!P9</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="3" t="str">
+        <f aca="false">NONCI_evt!Q9</f>
+        <v>0</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <f aca="false">NONCI_evt!R9</f>
+        <v>1</v>
+      </c>
+      <c r="L9" s="3" t="str">
+        <f aca="false">NONCI_vgp!P9</f>
+        <v>0</v>
+      </c>
+      <c r="M9" s="3" t="str">
+        <f aca="false">NONCI_vgp!Q9</f>
+        <v>0</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <f aca="false">NONCI_vgp!R9</f>
+        <v>1</v>
+      </c>
+      <c r="O9" s="10" t="n">
+        <f aca="false">IF(K9=N9,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P9" s="1" t="n">
+        <f aca="false">IF(O9=1,N(N9),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R9" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P9), ISERROR(Q9), P9="NA", Q9="NA"),
+   "NA",
+   N(P9) + N(Q9)
+)</f>
         <v>1</v>
       </c>
     </row>
@@ -15835,15 +17617,45 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4192845883494,2.19973194310656","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I10" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J10" s="1" t="str">
-        <f aca="false">IF(I10=1, NONCI_evt!R10, "")</f>
-        <v/>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>24</v>
+      <c r="I10" s="3" t="str">
+        <f aca="false">NONCI_evt!P10</f>
+        <v>NA</v>
+      </c>
+      <c r="J10" s="3" t="str">
+        <f aca="false">NONCI_evt!Q10</f>
+        <v>0</v>
+      </c>
+      <c r="K10" s="3" t="e">
+        <f aca="false">NONCI_evt!R10</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L10" s="3" t="str">
+        <f aca="false">NONCI_vgp!P10</f>
+        <v>NA</v>
+      </c>
+      <c r="M10" s="3" t="str">
+        <f aca="false">NONCI_vgp!Q10</f>
+        <v>0</v>
+      </c>
+      <c r="N10" s="3" t="e">
+        <f aca="false">NONCI_vgp!R10</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O10" s="10" t="e">
+        <f aca="false">IF(K10=N10,1,0)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P10" s="1" t="e">
+        <f aca="false">IF(O10=1,N(N10),"")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R10" s="1" t="e">
+        <f aca="false">IF(
+   OR(ISERROR(P10), ISERROR(Q10), P10="NA", Q10="NA"),
+   "NA",
+   N(P10) + N(Q10)
+)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15873,15 +17685,45 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.418314723108,2.20099660334155","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I11" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J11" s="1" t="str">
-        <f aca="false">IF(I11=1, NONCI_evt!R11, "")</f>
-        <v/>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>24</v>
+      <c r="I11" s="3" t="str">
+        <f aca="false">NONCI_evt!P11</f>
+        <v>NA</v>
+      </c>
+      <c r="J11" s="3" t="str">
+        <f aca="false">NONCI_evt!Q11</f>
+        <v>0</v>
+      </c>
+      <c r="K11" s="3" t="e">
+        <f aca="false">NONCI_evt!R11</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L11" s="3" t="str">
+        <f aca="false">NONCI_vgp!P11</f>
+        <v>NA</v>
+      </c>
+      <c r="M11" s="3" t="str">
+        <f aca="false">NONCI_vgp!Q11</f>
+        <v>0</v>
+      </c>
+      <c r="N11" s="3" t="e">
+        <f aca="false">NONCI_vgp!R11</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O11" s="10" t="e">
+        <f aca="false">IF(K11=N11,1,0)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P11" s="1" t="e">
+        <f aca="false">IF(O11=1,N(N11),"")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R11" s="1" t="e">
+        <f aca="false">IF(
+   OR(ISERROR(P11), ISERROR(Q11), P11="NA", Q11="NA"),
+   "NA",
+   N(P11) + N(Q11)
+)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15911,16 +17753,44 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4172851501864,2.1719534490003","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I12" s="10" t="n">
-        <f aca="false">IF(NONCI_evt!R12=NONCI_vgp!R12,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J12" s="21" t="b">
-        <f aca="false">IF(I12=1, NONCI_evt!R12, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K12" s="21" t="b">
-        <f aca="false">IF(I12=1, NONCI_evt!R12, "")</f>
+      <c r="I12" s="3" t="str">
+        <f aca="false">NONCI_evt!P12</f>
+        <v>0</v>
+      </c>
+      <c r="J12" s="3" t="str">
+        <f aca="false">NONCI_evt!Q12</f>
+        <v>0</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <f aca="false">NONCI_evt!R12</f>
+        <v>1</v>
+      </c>
+      <c r="L12" s="3" t="str">
+        <f aca="false">NONCI_vgp!P12</f>
+        <v>0</v>
+      </c>
+      <c r="M12" s="3" t="str">
+        <f aca="false">NONCI_vgp!Q12</f>
+        <v>0</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <f aca="false">NONCI_vgp!R12</f>
+        <v>1</v>
+      </c>
+      <c r="O12" s="10" t="n">
+        <f aca="false">IF(K12=N12,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P12" s="1" t="n">
+        <f aca="false">IF(O12=1,N(N12),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R12" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P12), ISERROR(Q12), P12="NA", Q12="NA"),
+   "NA",
+   N(P12) + N(Q12)
+)</f>
         <v>1</v>
       </c>
     </row>
@@ -15951,16 +17821,44 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4212327396107,2.2085959023376","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I13" s="10" t="n">
-        <f aca="false">IF(NONCI_evt!R13=NONCI_vgp!R13,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J13" s="21" t="b">
-        <f aca="false">IF(I13=1, NONCI_evt!R13, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K13" s="21" t="b">
-        <f aca="false">IF(I13=1, NONCI_evt!R13, "")</f>
+      <c r="I13" s="3" t="str">
+        <f aca="false">NONCI_evt!P13</f>
+        <v>0</v>
+      </c>
+      <c r="J13" s="3" t="str">
+        <f aca="false">NONCI_evt!Q13</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <f aca="false">NONCI_evt!R13</f>
+        <v>1</v>
+      </c>
+      <c r="L13" s="3" t="str">
+        <f aca="false">NONCI_vgp!P13</f>
+        <v>0</v>
+      </c>
+      <c r="M13" s="3" t="str">
+        <f aca="false">NONCI_vgp!Q13</f>
+        <v>0</v>
+      </c>
+      <c r="N13" s="3" t="n">
+        <f aca="false">NONCI_vgp!R13</f>
+        <v>1</v>
+      </c>
+      <c r="O13" s="10" t="n">
+        <f aca="false">IF(K13=N13,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P13" s="1" t="n">
+        <f aca="false">IF(O13=1,N(N13),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R13" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P13), ISERROR(Q13), P13="NA", Q13="NA"),
+   "NA",
+   N(P13) + N(Q13)
+)</f>
         <v>1</v>
       </c>
     </row>
@@ -15991,16 +17889,44 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4136824558834,2.16049369124227","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I14" s="10" t="n">
-        <f aca="false">IF(NONCI_evt!R14=NONCI_vgp!R14,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J14" s="21" t="b">
-        <f aca="false">IF(I14=1, NONCI_evt!R14, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K14" s="21" t="b">
-        <f aca="false">IF(I14=1, NONCI_evt!R14, "")</f>
+      <c r="I14" s="3" t="str">
+        <f aca="false">NONCI_evt!P14</f>
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="str">
+        <f aca="false">NONCI_evt!Q14</f>
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <f aca="false">NONCI_evt!R14</f>
+        <v>1</v>
+      </c>
+      <c r="L14" s="3" t="str">
+        <f aca="false">NONCI_vgp!P14</f>
+        <v>0</v>
+      </c>
+      <c r="M14" s="3" t="str">
+        <f aca="false">NONCI_vgp!Q14</f>
+        <v>0</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <f aca="false">NONCI_vgp!R14</f>
+        <v>1</v>
+      </c>
+      <c r="O14" s="10" t="n">
+        <f aca="false">IF(K14=N14,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P14" s="1" t="n">
+        <f aca="false">IF(O14=1,N(N14),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R14" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P14), ISERROR(Q14), P14="NA", Q14="NA"),
+   "NA",
+   N(P14) + N(Q14)
+)</f>
         <v>1</v>
       </c>
     </row>
@@ -16031,16 +17957,44 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3968741340237,2.19662757442697","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I15" s="10" t="n">
-        <f aca="false">IF(NONCI_evt!R15=NONCI_vgp!R15,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J15" s="21" t="b">
-        <f aca="false">IF(I15=1, NONCI_evt!R15, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K15" s="21" t="b">
-        <f aca="false">IF(I15=1, NONCI_evt!R15, "")</f>
+      <c r="I15" s="3" t="str">
+        <f aca="false">NONCI_evt!P15</f>
+        <v>0</v>
+      </c>
+      <c r="J15" s="3" t="str">
+        <f aca="false">NONCI_evt!Q15</f>
+        <v>0</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <f aca="false">NONCI_evt!R15</f>
+        <v>1</v>
+      </c>
+      <c r="L15" s="3" t="str">
+        <f aca="false">NONCI_vgp!P15</f>
+        <v>0</v>
+      </c>
+      <c r="M15" s="3" t="str">
+        <f aca="false">NONCI_vgp!Q15</f>
+        <v>0</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <f aca="false">NONCI_vgp!R15</f>
+        <v>1</v>
+      </c>
+      <c r="O15" s="10" t="n">
+        <f aca="false">IF(K15=N15,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P15" s="1" t="n">
+        <f aca="false">IF(O15=1,N(N15),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R15" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P15), ISERROR(Q15), P15="NA", Q15="NA"),
+   "NA",
+   N(P15) + N(Q15)
+)</f>
         <v>1</v>
       </c>
     </row>
@@ -16071,16 +18025,44 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3815198505021,2.17675959869425","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I16" s="10" t="n">
-        <f aca="false">IF(NONCI_evt!R16=NONCI_vgp!R16,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J16" s="21" t="b">
-        <f aca="false">IF(I16=1, NONCI_evt!R16, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K16" s="21" t="b">
-        <f aca="false">IF(I16=1, NONCI_evt!R16, "")</f>
+      <c r="I16" s="3" t="str">
+        <f aca="false">NONCI_evt!P16</f>
+        <v>0</v>
+      </c>
+      <c r="J16" s="3" t="str">
+        <f aca="false">NONCI_evt!Q16</f>
+        <v>0</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <f aca="false">NONCI_evt!R16</f>
+        <v>1</v>
+      </c>
+      <c r="L16" s="3" t="str">
+        <f aca="false">NONCI_vgp!P16</f>
+        <v>0</v>
+      </c>
+      <c r="M16" s="3" t="str">
+        <f aca="false">NONCI_vgp!Q16</f>
+        <v>0</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <f aca="false">NONCI_vgp!R16</f>
+        <v>1</v>
+      </c>
+      <c r="O16" s="10" t="n">
+        <f aca="false">IF(K16=N16,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P16" s="1" t="n">
+        <f aca="false">IF(O16=1,N(N16),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R16" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P16), ISERROR(Q16), P16="NA", Q16="NA"),
+   "NA",
+   N(P16) + N(Q16)
+)</f>
         <v>1</v>
       </c>
     </row>
@@ -16111,16 +18093,44 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3985654193142,2.19893423224654","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I17" s="10" t="n">
-        <f aca="false">IF(NONCI_evt!R17=NONCI_vgp!R17,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J17" s="21" t="b">
-        <f aca="false">IF(I17=1, NONCI_evt!R17, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K17" s="21" t="b">
-        <f aca="false">IF(I17=1, NONCI_evt!R17, "")</f>
+      <c r="I17" s="3" t="str">
+        <f aca="false">NONCI_evt!P17</f>
+        <v>0</v>
+      </c>
+      <c r="J17" s="3" t="str">
+        <f aca="false">NONCI_evt!Q17</f>
+        <v>0</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <f aca="false">NONCI_evt!R17</f>
+        <v>1</v>
+      </c>
+      <c r="L17" s="3" t="str">
+        <f aca="false">NONCI_vgp!P17</f>
+        <v>0</v>
+      </c>
+      <c r="M17" s="3" t="str">
+        <f aca="false">NONCI_vgp!Q17</f>
+        <v>0</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <f aca="false">NONCI_vgp!R17</f>
+        <v>1</v>
+      </c>
+      <c r="O17" s="10" t="n">
+        <f aca="false">IF(K17=N17,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P17" s="1" t="n">
+        <f aca="false">IF(O17=1,N(N17),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R17" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P17), ISERROR(Q17), P17="NA", Q17="NA"),
+   "NA",
+   N(P17) + N(Q17)
+)</f>
         <v>1</v>
       </c>
     </row>
@@ -16151,16 +18161,44 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4076066879062,2.20468220744704","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I18" s="10" t="n">
-        <f aca="false">IF(NONCI_evt!R18=NONCI_vgp!R18,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J18" s="21" t="b">
-        <f aca="false">IF(I18=1, NONCI_evt!R18, "")</f>
-        <v>0</v>
-      </c>
-      <c r="K18" s="21" t="b">
-        <f aca="false">IF(I18=1, NONCI_evt!R18, "")</f>
+      <c r="I18" s="3" t="str">
+        <f aca="false">NONCI_evt!P18</f>
+        <v>1</v>
+      </c>
+      <c r="J18" s="3" t="str">
+        <f aca="false">NONCI_evt!Q18</f>
+        <v>1</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <f aca="false">NONCI_evt!R18</f>
+        <v>0</v>
+      </c>
+      <c r="L18" s="3" t="str">
+        <f aca="false">NONCI_vgp!P18</f>
+        <v>1</v>
+      </c>
+      <c r="M18" s="3" t="str">
+        <f aca="false">NONCI_vgp!Q18</f>
+        <v>1</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <f aca="false">NONCI_vgp!R18</f>
+        <v>0</v>
+      </c>
+      <c r="O18" s="10" t="n">
+        <f aca="false">IF(K18=N18,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P18" s="1" t="n">
+        <f aca="false">IF(O18=1,N(N18),"")</f>
+        <v>0</v>
+      </c>
+      <c r="R18" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P18), ISERROR(Q18), P18="NA", Q18="NA"),
+   "NA",
+   N(P18) + N(Q18)
+)</f>
         <v>0</v>
       </c>
     </row>
@@ -16191,16 +18229,44 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3758934897395,2.14621758311762","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I19" s="10" t="n">
-        <f aca="false">IF(NONCI_evt!R19=NONCI_vgp!R19,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J19" s="21" t="b">
-        <f aca="false">IF(I19=1, NONCI_evt!R19, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K19" s="21" t="b">
-        <f aca="false">IF(I19=1, NONCI_evt!R19, "")</f>
+      <c r="I19" s="3" t="str">
+        <f aca="false">NONCI_evt!P19</f>
+        <v>0</v>
+      </c>
+      <c r="J19" s="3" t="str">
+        <f aca="false">NONCI_evt!Q19</f>
+        <v>0</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <f aca="false">NONCI_evt!R19</f>
+        <v>1</v>
+      </c>
+      <c r="L19" s="3" t="str">
+        <f aca="false">NONCI_vgp!P19</f>
+        <v>0</v>
+      </c>
+      <c r="M19" s="3" t="str">
+        <f aca="false">NONCI_vgp!Q19</f>
+        <v>0</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <f aca="false">NONCI_vgp!R19</f>
+        <v>1</v>
+      </c>
+      <c r="O19" s="10" t="n">
+        <f aca="false">IF(K19=N19,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P19" s="1" t="n">
+        <f aca="false">IF(O19=1,N(N19),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R19" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P19), ISERROR(Q19), P19="NA", Q19="NA"),
+   "NA",
+   N(P19) + N(Q19)
+)</f>
         <v>1</v>
       </c>
     </row>
@@ -16231,16 +18297,44 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.396230594351,2.1217889459586","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I20" s="10" t="n">
-        <f aca="false">IF(NONCI_evt!R20=NONCI_vgp!R20,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J20" s="21" t="b">
-        <f aca="false">IF(I20=1, NONCI_evt!R20, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K20" s="21" t="b">
-        <f aca="false">IF(I20=1, NONCI_evt!R20, "")</f>
+      <c r="I20" s="3" t="str">
+        <f aca="false">NONCI_evt!P20</f>
+        <v>0</v>
+      </c>
+      <c r="J20" s="3" t="str">
+        <f aca="false">NONCI_evt!Q20</f>
+        <v>0</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <f aca="false">NONCI_evt!R20</f>
+        <v>1</v>
+      </c>
+      <c r="L20" s="3" t="str">
+        <f aca="false">NONCI_vgp!P20</f>
+        <v>0</v>
+      </c>
+      <c r="M20" s="3" t="str">
+        <f aca="false">NONCI_vgp!Q20</f>
+        <v>0</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <f aca="false">NONCI_vgp!R20</f>
+        <v>1</v>
+      </c>
+      <c r="O20" s="10" t="n">
+        <f aca="false">IF(K20=N20,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P20" s="1" t="n">
+        <f aca="false">IF(O20=1,N(N20),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R20" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P20), ISERROR(Q20), P20="NA", Q20="NA"),
+   "NA",
+   N(P20) + N(Q20)
+)</f>
         <v>1</v>
       </c>
     </row>
@@ -16271,16 +18365,44 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4313457041624,2.17908894150395","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I21" s="10" t="n">
-        <f aca="false">IF(NONCI_evt!R21=NONCI_vgp!R21,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J21" s="21" t="b">
-        <f aca="false">IF(I21=1, NONCI_evt!R21, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K21" s="21" t="b">
-        <f aca="false">IF(I21=1, NONCI_evt!R21, "")</f>
+      <c r="I21" s="3" t="str">
+        <f aca="false">NONCI_evt!P21</f>
+        <v>0</v>
+      </c>
+      <c r="J21" s="3" t="str">
+        <f aca="false">NONCI_evt!Q21</f>
+        <v>0</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <f aca="false">NONCI_evt!R21</f>
+        <v>1</v>
+      </c>
+      <c r="L21" s="3" t="str">
+        <f aca="false">NONCI_vgp!P21</f>
+        <v>0</v>
+      </c>
+      <c r="M21" s="3" t="str">
+        <f aca="false">NONCI_vgp!Q21</f>
+        <v>0</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <f aca="false">NONCI_vgp!R21</f>
+        <v>1</v>
+      </c>
+      <c r="O21" s="10" t="n">
+        <f aca="false">IF(K21=N21,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P21" s="1" t="n">
+        <f aca="false">IF(O21=1,N(N21),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R21" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P21), ISERROR(Q21), P21="NA", Q21="NA"),
+   "NA",
+   N(P21) + N(Q21)
+)</f>
         <v>1</v>
       </c>
     </row>
@@ -16311,16 +18433,44 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3929009079565,2.1257689815069","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I22" s="10" t="n">
-        <f aca="false">IF(NONCI_evt!R22=NONCI_vgp!R22,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J22" s="21" t="b">
-        <f aca="false">IF(I22=1, NONCI_evt!R22, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K22" s="21" t="b">
-        <f aca="false">IF(I22=1, NONCI_evt!R22, "")</f>
+      <c r="I22" s="3" t="str">
+        <f aca="false">NONCI_evt!P22</f>
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="str">
+        <f aca="false">NONCI_evt!Q22</f>
+        <v>0</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <f aca="false">NONCI_evt!R22</f>
+        <v>1</v>
+      </c>
+      <c r="L22" s="3" t="str">
+        <f aca="false">NONCI_vgp!P22</f>
+        <v>0</v>
+      </c>
+      <c r="M22" s="3" t="str">
+        <f aca="false">NONCI_vgp!Q22</f>
+        <v>0</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <f aca="false">NONCI_vgp!R22</f>
+        <v>1</v>
+      </c>
+      <c r="O22" s="10" t="n">
+        <f aca="false">IF(K22=N22,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P22" s="1" t="n">
+        <f aca="false">IF(O22=1,N(N22),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R22" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P22), ISERROR(Q22), P22="NA", Q22="NA"),
+   "NA",
+   N(P22) + N(Q22)
+)</f>
         <v>1</v>
       </c>
     </row>
@@ -16351,16 +18501,44 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4348652360132,2.18422140795697","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I23" s="10" t="n">
-        <f aca="false">IF(NONCI_evt!R23=NONCI_vgp!R23,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J23" s="21" t="b">
-        <f aca="false">IF(I23=1, NONCI_evt!R23, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K23" s="21" t="b">
-        <f aca="false">IF(I23=1, NONCI_evt!R23, "")</f>
+      <c r="I23" s="3" t="str">
+        <f aca="false">NONCI_evt!P23</f>
+        <v>0</v>
+      </c>
+      <c r="J23" s="3" t="str">
+        <f aca="false">NONCI_evt!Q23</f>
+        <v>0</v>
+      </c>
+      <c r="K23" s="3" t="n">
+        <f aca="false">NONCI_evt!R23</f>
+        <v>1</v>
+      </c>
+      <c r="L23" s="3" t="str">
+        <f aca="false">NONCI_vgp!P23</f>
+        <v>0</v>
+      </c>
+      <c r="M23" s="3" t="str">
+        <f aca="false">NONCI_vgp!Q23</f>
+        <v>0</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <f aca="false">NONCI_vgp!R23</f>
+        <v>1</v>
+      </c>
+      <c r="O23" s="10" t="n">
+        <f aca="false">IF(K23=N23,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P23" s="1" t="n">
+        <f aca="false">IF(O23=1,N(N23),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R23" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P23), ISERROR(Q23), P23="NA", Q23="NA"),
+   "NA",
+   N(P23) + N(Q23)
+)</f>
         <v>1</v>
       </c>
     </row>
@@ -16391,19 +18569,48 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4280696452023,2.17554070368043","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I24" s="10" t="n">
-        <f aca="false">IF(NONCI_evt!R24=NONCI_vgp!R24,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="J24" s="1" t="str">
-        <f aca="false">IF(I24=1, NONCI_evt!R24, "")</f>
+      <c r="I24" s="3" t="str">
+        <f aca="false">NONCI_evt!P24</f>
+        <v>0</v>
+      </c>
+      <c r="J24" s="3" t="str">
+        <f aca="false">NONCI_evt!Q24</f>
+        <v>0</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <f aca="false">NONCI_evt!R24</f>
+        <v>1</v>
+      </c>
+      <c r="L24" s="3" t="str">
+        <f aca="false">NONCI_vgp!P24</f>
+        <v>1</v>
+      </c>
+      <c r="M24" s="3" t="str">
+        <f aca="false">NONCI_vgp!Q24</f>
+        <v>1</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <f aca="false">NONCI_vgp!R24</f>
+        <v>0</v>
+      </c>
+      <c r="O24" s="10" t="n">
+        <f aca="false">IF(K24=N24,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="P24" s="1" t="str">
+        <f aca="false">IF(O24=1,N(N24),"")</f>
         <v/>
       </c>
-      <c r="K24" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="1" t="s">
-        <v>257</v>
+      <c r="R24" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P24), ISERROR(Q24), P24="NA", Q24="NA"),
+   "NA",
+   N(P24) + N(Q24)
+)</f>
+        <v>0</v>
+      </c>
+      <c r="S24" s="1" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16433,16 +18640,44 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4407613525245,2.18916874931851","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I25" s="10" t="n">
-        <f aca="false">IF(NONCI_evt!R25=NONCI_vgp!R25,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J25" s="21" t="b">
-        <f aca="false">IF(I25=1, NONCI_evt!R25, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K25" s="21" t="b">
-        <f aca="false">IF(I25=1, NONCI_evt!R25, "")</f>
+      <c r="I25" s="3" t="str">
+        <f aca="false">NONCI_evt!P25</f>
+        <v>0</v>
+      </c>
+      <c r="J25" s="3" t="str">
+        <f aca="false">NONCI_evt!Q25</f>
+        <v>0</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <f aca="false">NONCI_evt!R25</f>
+        <v>1</v>
+      </c>
+      <c r="L25" s="3" t="str">
+        <f aca="false">NONCI_vgp!P25</f>
+        <v>0</v>
+      </c>
+      <c r="M25" s="3" t="str">
+        <f aca="false">NONCI_vgp!Q25</f>
+        <v>0</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <f aca="false">NONCI_vgp!R25</f>
+        <v>1</v>
+      </c>
+      <c r="O25" s="10" t="n">
+        <f aca="false">IF(K25=N25,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P25" s="1" t="n">
+        <f aca="false">IF(O25=1,N(N25),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R25" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P25), ISERROR(Q25), P25="NA", Q25="NA"),
+   "NA",
+   N(P25) + N(Q25)
+)</f>
         <v>1</v>
       </c>
     </row>
@@ -16473,16 +18708,44 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4011854588709,2.15235610314992","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I26" s="10" t="n">
-        <f aca="false">IF(NONCI_evt!R26=NONCI_vgp!R26,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J26" s="21" t="b">
-        <f aca="false">IF(I26=1, NONCI_evt!R26, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K26" s="21" t="b">
-        <f aca="false">IF(I26=1, NONCI_evt!R26, "")</f>
+      <c r="I26" s="3" t="str">
+        <f aca="false">NONCI_evt!P26</f>
+        <v>0</v>
+      </c>
+      <c r="J26" s="3" t="str">
+        <f aca="false">NONCI_evt!Q26</f>
+        <v>0</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <f aca="false">NONCI_evt!R26</f>
+        <v>1</v>
+      </c>
+      <c r="L26" s="3" t="str">
+        <f aca="false">NONCI_vgp!P26</f>
+        <v>0</v>
+      </c>
+      <c r="M26" s="3" t="str">
+        <f aca="false">NONCI_vgp!Q26</f>
+        <v>0</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <f aca="false">NONCI_vgp!R26</f>
+        <v>1</v>
+      </c>
+      <c r="O26" s="10" t="n">
+        <f aca="false">IF(K26=N26,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P26" s="1" t="n">
+        <f aca="false">IF(O26=1,N(N26),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R26" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P26), ISERROR(Q26), P26="NA", Q26="NA"),
+   "NA",
+   N(P26) + N(Q26)
+)</f>
         <v>1</v>
       </c>
     </row>
@@ -16513,16 +18776,44 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4010048500573,2.13609114981908","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I27" s="10" t="n">
-        <f aca="false">IF(NONCI_evt!R27=NONCI_vgp!R27,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J27" s="21" t="b">
-        <f aca="false">IF(I27=1, NONCI_evt!R27, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K27" s="21" t="b">
-        <f aca="false">IF(I27=1, NONCI_evt!R27, "")</f>
+      <c r="I27" s="3" t="str">
+        <f aca="false">NONCI_evt!P27</f>
+        <v>0</v>
+      </c>
+      <c r="J27" s="3" t="str">
+        <f aca="false">NONCI_evt!Q27</f>
+        <v>0</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <f aca="false">NONCI_evt!R27</f>
+        <v>1</v>
+      </c>
+      <c r="L27" s="3" t="str">
+        <f aca="false">NONCI_vgp!P27</f>
+        <v>0</v>
+      </c>
+      <c r="M27" s="3" t="str">
+        <f aca="false">NONCI_vgp!Q27</f>
+        <v>0</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <f aca="false">NONCI_vgp!R27</f>
+        <v>1</v>
+      </c>
+      <c r="O27" s="10" t="n">
+        <f aca="false">IF(K27=N27,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P27" s="1" t="n">
+        <f aca="false">IF(O27=1,N(N27),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R27" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P27), ISERROR(Q27), P27="NA", Q27="NA"),
+   "NA",
+   N(P27) + N(Q27)
+)</f>
         <v>1</v>
       </c>
     </row>
@@ -16553,16 +18844,44 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4226246930358,2.17196473004792","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I28" s="10" t="n">
-        <f aca="false">IF(NONCI_evt!R28=NONCI_vgp!R28,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J28" s="21" t="b">
-        <f aca="false">IF(I28=1, NONCI_evt!R28, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K28" s="21" t="b">
-        <f aca="false">IF(I28=1, NONCI_evt!R28, "")</f>
+      <c r="I28" s="3" t="str">
+        <f aca="false">NONCI_evt!P28</f>
+        <v>0</v>
+      </c>
+      <c r="J28" s="3" t="str">
+        <f aca="false">NONCI_evt!Q28</f>
+        <v>0</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <f aca="false">NONCI_evt!R28</f>
+        <v>1</v>
+      </c>
+      <c r="L28" s="3" t="str">
+        <f aca="false">NONCI_vgp!P28</f>
+        <v>0</v>
+      </c>
+      <c r="M28" s="3" t="str">
+        <f aca="false">NONCI_vgp!Q28</f>
+        <v>0</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <f aca="false">NONCI_vgp!R28</f>
+        <v>1</v>
+      </c>
+      <c r="O28" s="10" t="n">
+        <f aca="false">IF(K28=N28,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P28" s="1" t="n">
+        <f aca="false">IF(O28=1,N(N28),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R28" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P28), ISERROR(Q28), P28="NA", Q28="NA"),
+   "NA",
+   N(P28) + N(Q28)
+)</f>
         <v>1</v>
       </c>
     </row>
@@ -16593,16 +18912,44 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4132997449837,2.18467735930514","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I29" s="10" t="n">
-        <f aca="false">IF(NONCI_evt!R29=NONCI_vgp!R29,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J29" s="21" t="b">
-        <f aca="false">IF(I29=1, NONCI_evt!R29, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K29" s="21" t="b">
-        <f aca="false">IF(I29=1, NONCI_evt!R29, "")</f>
+      <c r="I29" s="3" t="str">
+        <f aca="false">NONCI_evt!P29</f>
+        <v>0</v>
+      </c>
+      <c r="J29" s="3" t="str">
+        <f aca="false">NONCI_evt!Q29</f>
+        <v>0</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <f aca="false">NONCI_evt!R29</f>
+        <v>1</v>
+      </c>
+      <c r="L29" s="3" t="str">
+        <f aca="false">NONCI_vgp!P29</f>
+        <v>0</v>
+      </c>
+      <c r="M29" s="3" t="str">
+        <f aca="false">NONCI_vgp!Q29</f>
+        <v>0</v>
+      </c>
+      <c r="N29" s="3" t="n">
+        <f aca="false">NONCI_vgp!R29</f>
+        <v>1</v>
+      </c>
+      <c r="O29" s="10" t="n">
+        <f aca="false">IF(K29=N29,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P29" s="1" t="n">
+        <f aca="false">IF(O29=1,N(N29),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R29" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P29), ISERROR(Q29), P29="NA", Q29="NA"),
+   "NA",
+   N(P29) + N(Q29)
+)</f>
         <v>1</v>
       </c>
     </row>
@@ -16633,16 +18980,44 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4057193003193,2.1562834011384","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I30" s="10" t="n">
-        <f aca="false">IF(NONCI_evt!R30=NONCI_vgp!R30,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J30" s="21" t="b">
-        <f aca="false">IF(I30=1, NONCI_evt!R30, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K30" s="21" t="b">
-        <f aca="false">IF(I30=1, NONCI_evt!R30, "")</f>
+      <c r="I30" s="3" t="str">
+        <f aca="false">NONCI_evt!P30</f>
+        <v>0</v>
+      </c>
+      <c r="J30" s="3" t="str">
+        <f aca="false">NONCI_evt!Q30</f>
+        <v>0</v>
+      </c>
+      <c r="K30" s="3" t="n">
+        <f aca="false">NONCI_evt!R30</f>
+        <v>1</v>
+      </c>
+      <c r="L30" s="3" t="str">
+        <f aca="false">NONCI_vgp!P30</f>
+        <v>0</v>
+      </c>
+      <c r="M30" s="3" t="str">
+        <f aca="false">NONCI_vgp!Q30</f>
+        <v>0</v>
+      </c>
+      <c r="N30" s="3" t="n">
+        <f aca="false">NONCI_vgp!R30</f>
+        <v>1</v>
+      </c>
+      <c r="O30" s="10" t="n">
+        <f aca="false">IF(K30=N30,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P30" s="1" t="n">
+        <f aca="false">IF(O30=1,N(N30),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R30" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P30), ISERROR(Q30), P30="NA", Q30="NA"),
+   "NA",
+   N(P30) + N(Q30)
+)</f>
         <v>1</v>
       </c>
     </row>
@@ -16673,16 +19048,44 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3872125901025,2.13581324384167","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I31" s="10" t="n">
-        <f aca="false">IF(NONCI_evt!R31=NONCI_vgp!R31,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J31" s="21" t="b">
-        <f aca="false">IF(I31=1, NONCI_evt!R31, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K31" s="21" t="b">
-        <f aca="false">IF(I31=1, NONCI_evt!R31, "")</f>
+      <c r="I31" s="3" t="str">
+        <f aca="false">NONCI_evt!P31</f>
+        <v>0</v>
+      </c>
+      <c r="J31" s="3" t="str">
+        <f aca="false">NONCI_evt!Q31</f>
+        <v>0</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <f aca="false">NONCI_evt!R31</f>
+        <v>1</v>
+      </c>
+      <c r="L31" s="3" t="str">
+        <f aca="false">NONCI_vgp!P31</f>
+        <v>0</v>
+      </c>
+      <c r="M31" s="3" t="str">
+        <f aca="false">NONCI_vgp!Q31</f>
+        <v>0</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <f aca="false">NONCI_vgp!R31</f>
+        <v>1</v>
+      </c>
+      <c r="O31" s="10" t="n">
+        <f aca="false">IF(K31=N31,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P31" s="1" t="n">
+        <f aca="false">IF(O31=1,N(N31),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R31" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P31), ISERROR(Q31), P31="NA", Q31="NA"),
+   "NA",
+   N(P31) + N(Q31)
+)</f>
         <v>1</v>
       </c>
     </row>
@@ -16713,16 +19116,44 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.391080594057,2.18509796710136","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I32" s="10" t="n">
-        <f aca="false">IF(NONCI_evt!R32=NONCI_vgp!R32,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J32" s="21" t="b">
-        <f aca="false">IF(I32=1, NONCI_evt!R32, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K32" s="21" t="b">
-        <f aca="false">IF(I32=1, NONCI_evt!R32, "")</f>
+      <c r="I32" s="3" t="str">
+        <f aca="false">NONCI_evt!P32</f>
+        <v>0</v>
+      </c>
+      <c r="J32" s="3" t="str">
+        <f aca="false">NONCI_evt!Q32</f>
+        <v>0</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <f aca="false">NONCI_evt!R32</f>
+        <v>1</v>
+      </c>
+      <c r="L32" s="3" t="str">
+        <f aca="false">NONCI_vgp!P32</f>
+        <v>0</v>
+      </c>
+      <c r="M32" s="3" t="str">
+        <f aca="false">NONCI_vgp!Q32</f>
+        <v>0</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <f aca="false">NONCI_vgp!R32</f>
+        <v>1</v>
+      </c>
+      <c r="O32" s="10" t="n">
+        <f aca="false">IF(K32=N32,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P32" s="1" t="n">
+        <f aca="false">IF(O32=1,N(N32),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R32" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P32), ISERROR(Q32), P32="NA", Q32="NA"),
+   "NA",
+   N(P32) + N(Q32)
+)</f>
         <v>1</v>
       </c>
     </row>
@@ -16753,16 +19184,44 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4011555199841,2.20237586249134","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I33" s="10" t="n">
-        <f aca="false">IF(NONCI_evt!R33=NONCI_vgp!R33,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J33" s="21" t="b">
-        <f aca="false">IF(I33=1, NONCI_evt!R33, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K33" s="21" t="b">
-        <f aca="false">IF(I33=1, NONCI_evt!R33, "")</f>
+      <c r="I33" s="3" t="str">
+        <f aca="false">NONCI_evt!P33</f>
+        <v>0</v>
+      </c>
+      <c r="J33" s="3" t="str">
+        <f aca="false">NONCI_evt!Q33</f>
+        <v>0</v>
+      </c>
+      <c r="K33" s="3" t="n">
+        <f aca="false">NONCI_evt!R33</f>
+        <v>1</v>
+      </c>
+      <c r="L33" s="3" t="str">
+        <f aca="false">NONCI_vgp!P33</f>
+        <v>0</v>
+      </c>
+      <c r="M33" s="3" t="str">
+        <f aca="false">NONCI_vgp!Q33</f>
+        <v>0</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <f aca="false">NONCI_vgp!R33</f>
+        <v>1</v>
+      </c>
+      <c r="O33" s="10" t="n">
+        <f aca="false">IF(K33=N33,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P33" s="1" t="n">
+        <f aca="false">IF(O33=1,N(N33),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R33" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P33), ISERROR(Q33), P33="NA", Q33="NA"),
+   "NA",
+   N(P33) + N(Q33)
+)</f>
         <v>1</v>
       </c>
     </row>
@@ -16793,16 +19252,44 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3800730268472,2.19139544456942","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I34" s="10" t="n">
-        <f aca="false">IF(NONCI_evt!R34=NONCI_vgp!R34,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J34" s="21" t="b">
-        <f aca="false">IF(I34=1, NONCI_evt!R34, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K34" s="21" t="b">
-        <f aca="false">IF(I34=1, NONCI_evt!R34, "")</f>
+      <c r="I34" s="3" t="str">
+        <f aca="false">NONCI_evt!P34</f>
+        <v>0</v>
+      </c>
+      <c r="J34" s="3" t="str">
+        <f aca="false">NONCI_evt!Q34</f>
+        <v>0</v>
+      </c>
+      <c r="K34" s="3" t="n">
+        <f aca="false">NONCI_evt!R34</f>
+        <v>1</v>
+      </c>
+      <c r="L34" s="3" t="str">
+        <f aca="false">NONCI_vgp!P34</f>
+        <v>0</v>
+      </c>
+      <c r="M34" s="3" t="str">
+        <f aca="false">NONCI_vgp!Q34</f>
+        <v>0</v>
+      </c>
+      <c r="N34" s="3" t="n">
+        <f aca="false">NONCI_vgp!R34</f>
+        <v>1</v>
+      </c>
+      <c r="O34" s="10" t="n">
+        <f aca="false">IF(K34=N34,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P34" s="1" t="n">
+        <f aca="false">IF(O34=1,N(N34),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R34" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P34), ISERROR(Q34), P34="NA", Q34="NA"),
+   "NA",
+   N(P34) + N(Q34)
+)</f>
         <v>1</v>
       </c>
     </row>
@@ -16833,16 +19320,44 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3843067005011,2.1831528971609","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I35" s="10" t="n">
-        <f aca="false">IF(NONCI_evt!R35=NONCI_vgp!R35,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J35" s="21" t="b">
-        <f aca="false">IF(I35=1, NONCI_evt!R35, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K35" s="21" t="b">
-        <f aca="false">IF(I35=1, NONCI_evt!R35, "")</f>
+      <c r="I35" s="3" t="str">
+        <f aca="false">NONCI_evt!P35</f>
+        <v>0</v>
+      </c>
+      <c r="J35" s="3" t="str">
+        <f aca="false">NONCI_evt!Q35</f>
+        <v>0</v>
+      </c>
+      <c r="K35" s="3" t="n">
+        <f aca="false">NONCI_evt!R35</f>
+        <v>1</v>
+      </c>
+      <c r="L35" s="3" t="str">
+        <f aca="false">NONCI_vgp!P35</f>
+        <v>0</v>
+      </c>
+      <c r="M35" s="3" t="str">
+        <f aca="false">NONCI_vgp!Q35</f>
+        <v>0</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <f aca="false">NONCI_vgp!R35</f>
+        <v>1</v>
+      </c>
+      <c r="O35" s="10" t="n">
+        <f aca="false">IF(K35=N35,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P35" s="1" t="n">
+        <f aca="false">IF(O35=1,N(N35),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R35" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P35), ISERROR(Q35), P35="NA", Q35="NA"),
+   "NA",
+   N(P35) + N(Q35)
+)</f>
         <v>1</v>
       </c>
     </row>
@@ -16873,15 +19388,45 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3983624631247,2.15678942388002","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I36" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J36" s="1" t="str">
-        <f aca="false">IF(I36=1, NONCI_evt!R36, "")</f>
-        <v/>
-      </c>
-      <c r="K36" s="1" t="s">
-        <v>24</v>
+      <c r="I36" s="3" t="str">
+        <f aca="false">NONCI_evt!P36</f>
+        <v>NA</v>
+      </c>
+      <c r="J36" s="3" t="str">
+        <f aca="false">NONCI_evt!Q36</f>
+        <v>NA</v>
+      </c>
+      <c r="K36" s="3" t="e">
+        <f aca="false">NONCI_evt!R36</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L36" s="3" t="str">
+        <f aca="false">NONCI_vgp!P36</f>
+        <v>NA</v>
+      </c>
+      <c r="M36" s="3" t="str">
+        <f aca="false">NONCI_vgp!Q36</f>
+        <v>NA</v>
+      </c>
+      <c r="N36" s="3" t="e">
+        <f aca="false">NONCI_vgp!R36</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O36" s="10" t="e">
+        <f aca="false">IF(K36=N36,1,0)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P36" s="1" t="e">
+        <f aca="false">IF(O36=1,N(N36),"")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R36" s="1" t="e">
+        <f aca="false">IF(
+   OR(ISERROR(P36), ISERROR(Q36), P36="NA", Q36="NA"),
+   "NA",
+   N(P36) + N(Q36)
+)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16911,16 +19456,44 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4113466536383,2.14114636598878","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I37" s="10" t="n">
-        <f aca="false">IF(NONCI_evt!R37=NONCI_vgp!R37,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J37" s="21" t="b">
-        <f aca="false">IF(I37=1, NONCI_evt!R37, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K37" s="21" t="b">
-        <f aca="false">IF(I37=1, NONCI_evt!R37, "")</f>
+      <c r="I37" s="3" t="str">
+        <f aca="false">NONCI_evt!P37</f>
+        <v>0</v>
+      </c>
+      <c r="J37" s="3" t="str">
+        <f aca="false">NONCI_evt!Q37</f>
+        <v>0</v>
+      </c>
+      <c r="K37" s="3" t="n">
+        <f aca="false">NONCI_evt!R37</f>
+        <v>1</v>
+      </c>
+      <c r="L37" s="3" t="str">
+        <f aca="false">NONCI_vgp!P37</f>
+        <v>0</v>
+      </c>
+      <c r="M37" s="3" t="str">
+        <f aca="false">NONCI_vgp!Q37</f>
+        <v>0</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <f aca="false">NONCI_vgp!R37</f>
+        <v>1</v>
+      </c>
+      <c r="O37" s="10" t="n">
+        <f aca="false">IF(K37=N37,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P37" s="1" t="n">
+        <f aca="false">IF(O37=1,N(N37),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R37" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P37), ISERROR(Q37), P37="NA", Q37="NA"),
+   "NA",
+   N(P37) + N(Q37)
+)</f>
         <v>1</v>
       </c>
     </row>
@@ -16951,16 +19524,44 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.426135711319,2.17240513302861","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I38" s="10" t="n">
-        <f aca="false">IF(NONCI_evt!R38=NONCI_vgp!R38,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J38" s="21" t="b">
-        <f aca="false">IF(I38=1, NONCI_evt!R38, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K38" s="21" t="b">
-        <f aca="false">IF(I38=1, NONCI_evt!R38, "")</f>
+      <c r="I38" s="3" t="str">
+        <f aca="false">NONCI_evt!P38</f>
+        <v>0</v>
+      </c>
+      <c r="J38" s="3" t="str">
+        <f aca="false">NONCI_evt!Q38</f>
+        <v>0</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <f aca="false">NONCI_evt!R38</f>
+        <v>1</v>
+      </c>
+      <c r="L38" s="3" t="str">
+        <f aca="false">NONCI_vgp!P38</f>
+        <v>0</v>
+      </c>
+      <c r="M38" s="3" t="str">
+        <f aca="false">NONCI_vgp!Q38</f>
+        <v>0</v>
+      </c>
+      <c r="N38" s="3" t="n">
+        <f aca="false">NONCI_vgp!R38</f>
+        <v>1</v>
+      </c>
+      <c r="O38" s="10" t="n">
+        <f aca="false">IF(K38=N38,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P38" s="1" t="n">
+        <f aca="false">IF(O38=1,N(N38),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R38" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P38), ISERROR(Q38), P38="NA", Q38="NA"),
+   "NA",
+   N(P38) + N(Q38)
+)</f>
         <v>1</v>
       </c>
     </row>
@@ -16991,16 +19592,44 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4375909606213,2.17558434676366","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I39" s="10" t="n">
-        <f aca="false">IF(NONCI_evt!R39=NONCI_vgp!R39,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J39" s="21" t="b">
-        <f aca="false">IF(I39=1, NONCI_evt!R39, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K39" s="21" t="b">
-        <f aca="false">IF(I39=1, NONCI_evt!R39, "")</f>
+      <c r="I39" s="3" t="str">
+        <f aca="false">NONCI_evt!P39</f>
+        <v>0</v>
+      </c>
+      <c r="J39" s="3" t="str">
+        <f aca="false">NONCI_evt!Q39</f>
+        <v>0</v>
+      </c>
+      <c r="K39" s="3" t="n">
+        <f aca="false">NONCI_evt!R39</f>
+        <v>1</v>
+      </c>
+      <c r="L39" s="3" t="str">
+        <f aca="false">NONCI_vgp!P39</f>
+        <v>0</v>
+      </c>
+      <c r="M39" s="3" t="str">
+        <f aca="false">NONCI_vgp!Q39</f>
+        <v>0</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <f aca="false">NONCI_vgp!R39</f>
+        <v>1</v>
+      </c>
+      <c r="O39" s="10" t="n">
+        <f aca="false">IF(K39=N39,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P39" s="1" t="n">
+        <f aca="false">IF(O39=1,N(N39),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R39" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P39), ISERROR(Q39), P39="NA", Q39="NA"),
+   "NA",
+   N(P39) + N(Q39)
+)</f>
         <v>1</v>
       </c>
     </row>
@@ -17031,16 +19660,44 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4283525000278,2.172146050328","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I40" s="10" t="n">
-        <f aca="false">IF(NONCI_evt!R40=NONCI_vgp!R40,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J40" s="21" t="b">
-        <f aca="false">IF(I40=1, NONCI_evt!R40, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K40" s="21" t="b">
-        <f aca="false">IF(I40=1, NONCI_evt!R40, "")</f>
+      <c r="I40" s="3" t="str">
+        <f aca="false">NONCI_evt!P40</f>
+        <v>0</v>
+      </c>
+      <c r="J40" s="3" t="str">
+        <f aca="false">NONCI_evt!Q40</f>
+        <v>0</v>
+      </c>
+      <c r="K40" s="3" t="n">
+        <f aca="false">NONCI_evt!R40</f>
+        <v>1</v>
+      </c>
+      <c r="L40" s="3" t="str">
+        <f aca="false">NONCI_vgp!P40</f>
+        <v>0</v>
+      </c>
+      <c r="M40" s="3" t="str">
+        <f aca="false">NONCI_vgp!Q40</f>
+        <v>0</v>
+      </c>
+      <c r="N40" s="3" t="n">
+        <f aca="false">NONCI_vgp!R40</f>
+        <v>1</v>
+      </c>
+      <c r="O40" s="10" t="n">
+        <f aca="false">IF(K40=N40,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P40" s="1" t="n">
+        <f aca="false">IF(O40=1,N(N40),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R40" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P40), ISERROR(Q40), P40="NA", Q40="NA"),
+   "NA",
+   N(P40) + N(Q40)
+)</f>
         <v>1</v>
       </c>
     </row>
@@ -17071,16 +19728,44 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3762841412853,2.12497775693313","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I41" s="10" t="n">
-        <f aca="false">IF(NONCI_evt!R41=NONCI_vgp!R41,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J41" s="21" t="b">
-        <f aca="false">IF(I41=1, NONCI_evt!R41, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K41" s="21" t="b">
-        <f aca="false">IF(I41=1, NONCI_evt!R41, "")</f>
+      <c r="I41" s="3" t="str">
+        <f aca="false">NONCI_evt!P41</f>
+        <v>0</v>
+      </c>
+      <c r="J41" s="3" t="str">
+        <f aca="false">NONCI_evt!Q41</f>
+        <v>0</v>
+      </c>
+      <c r="K41" s="3" t="n">
+        <f aca="false">NONCI_evt!R41</f>
+        <v>1</v>
+      </c>
+      <c r="L41" s="3" t="str">
+        <f aca="false">NONCI_vgp!P41</f>
+        <v>0</v>
+      </c>
+      <c r="M41" s="3" t="str">
+        <f aca="false">NONCI_vgp!Q41</f>
+        <v>0</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <f aca="false">NONCI_vgp!R41</f>
+        <v>1</v>
+      </c>
+      <c r="O41" s="10" t="n">
+        <f aca="false">IF(K41=N41,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P41" s="1" t="n">
+        <f aca="false">IF(O41=1,N(N41),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R41" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P41), ISERROR(Q41), P41="NA", Q41="NA"),
+   "NA",
+   N(P41) + N(Q41)
+)</f>
         <v>1</v>
       </c>
     </row>
@@ -17111,16 +19796,44 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3747198157894,2.13175238117479","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I42" s="10" t="n">
-        <f aca="false">IF(NONCI_evt!R42=NONCI_vgp!R42,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J42" s="21" t="b">
-        <f aca="false">IF(I42=1, NONCI_evt!R42, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K42" s="21" t="b">
-        <f aca="false">IF(I42=1, NONCI_evt!R42, "")</f>
+      <c r="I42" s="3" t="str">
+        <f aca="false">NONCI_evt!P42</f>
+        <v>0</v>
+      </c>
+      <c r="J42" s="3" t="str">
+        <f aca="false">NONCI_evt!Q42</f>
+        <v>0</v>
+      </c>
+      <c r="K42" s="3" t="n">
+        <f aca="false">NONCI_evt!R42</f>
+        <v>1</v>
+      </c>
+      <c r="L42" s="3" t="str">
+        <f aca="false">NONCI_vgp!P42</f>
+        <v>0</v>
+      </c>
+      <c r="M42" s="3" t="str">
+        <f aca="false">NONCI_vgp!Q42</f>
+        <v>0</v>
+      </c>
+      <c r="N42" s="3" t="n">
+        <f aca="false">NONCI_vgp!R42</f>
+        <v>1</v>
+      </c>
+      <c r="O42" s="10" t="n">
+        <f aca="false">IF(K42=N42,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P42" s="1" t="n">
+        <f aca="false">IF(O42=1,N(N42),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R42" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P42), ISERROR(Q42), P42="NA", Q42="NA"),
+   "NA",
+   N(P42) + N(Q42)
+)</f>
         <v>1</v>
       </c>
     </row>
@@ -17151,16 +19864,44 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4130107880215,2.17998387981679","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I43" s="10" t="n">
-        <f aca="false">IF(NONCI_evt!R43=NONCI_vgp!R43,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J43" s="21" t="b">
-        <f aca="false">IF(I43=1, NONCI_evt!R43, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K43" s="21" t="b">
-        <f aca="false">IF(I43=1, NONCI_evt!R43, "")</f>
+      <c r="I43" s="3" t="str">
+        <f aca="false">NONCI_evt!P43</f>
+        <v>0</v>
+      </c>
+      <c r="J43" s="3" t="str">
+        <f aca="false">NONCI_evt!Q43</f>
+        <v>0</v>
+      </c>
+      <c r="K43" s="3" t="n">
+        <f aca="false">NONCI_evt!R43</f>
+        <v>1</v>
+      </c>
+      <c r="L43" s="3" t="str">
+        <f aca="false">NONCI_vgp!P43</f>
+        <v>0</v>
+      </c>
+      <c r="M43" s="3" t="str">
+        <f aca="false">NONCI_vgp!Q43</f>
+        <v>0</v>
+      </c>
+      <c r="N43" s="3" t="n">
+        <f aca="false">NONCI_vgp!R43</f>
+        <v>1</v>
+      </c>
+      <c r="O43" s="10" t="n">
+        <f aca="false">IF(K43=N43,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P43" s="1" t="n">
+        <f aca="false">IF(O43=1,N(N43),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R43" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P43), ISERROR(Q43), P43="NA", Q43="NA"),
+   "NA",
+   N(P43) + N(Q43)
+)</f>
         <v>1</v>
       </c>
     </row>
@@ -17191,16 +19932,44 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3837233079119,2.13746672328433","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I44" s="10" t="n">
-        <f aca="false">IF(NONCI_evt!R44=NONCI_vgp!R44,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J44" s="21" t="b">
-        <f aca="false">IF(I44=1, NONCI_evt!R44, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K44" s="21" t="b">
-        <f aca="false">IF(I44=1, NONCI_evt!R44, "")</f>
+      <c r="I44" s="3" t="str">
+        <f aca="false">NONCI_evt!P44</f>
+        <v>0</v>
+      </c>
+      <c r="J44" s="3" t="str">
+        <f aca="false">NONCI_evt!Q44</f>
+        <v>0</v>
+      </c>
+      <c r="K44" s="3" t="n">
+        <f aca="false">NONCI_evt!R44</f>
+        <v>1</v>
+      </c>
+      <c r="L44" s="3" t="str">
+        <f aca="false">NONCI_vgp!P44</f>
+        <v>0</v>
+      </c>
+      <c r="M44" s="3" t="str">
+        <f aca="false">NONCI_vgp!Q44</f>
+        <v>0</v>
+      </c>
+      <c r="N44" s="3" t="n">
+        <f aca="false">NONCI_vgp!R44</f>
+        <v>1</v>
+      </c>
+      <c r="O44" s="10" t="n">
+        <f aca="false">IF(K44=N44,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P44" s="1" t="n">
+        <f aca="false">IF(O44=1,N(N44),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R44" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P44), ISERROR(Q44), P44="NA", Q44="NA"),
+   "NA",
+   N(P44) + N(Q44)
+)</f>
         <v>1</v>
       </c>
     </row>
@@ -17231,16 +20000,44 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4180150021324,2.18877627141089","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I45" s="10" t="n">
-        <f aca="false">IF(NONCI_evt!R45=NONCI_vgp!R45,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J45" s="21" t="b">
-        <f aca="false">IF(I45=1, NONCI_evt!R45, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K45" s="21" t="b">
-        <f aca="false">IF(I45=1, NONCI_evt!R45, "")</f>
+      <c r="I45" s="3" t="str">
+        <f aca="false">NONCI_evt!P45</f>
+        <v>0</v>
+      </c>
+      <c r="J45" s="3" t="str">
+        <f aca="false">NONCI_evt!Q45</f>
+        <v>0</v>
+      </c>
+      <c r="K45" s="3" t="n">
+        <f aca="false">NONCI_evt!R45</f>
+        <v>1</v>
+      </c>
+      <c r="L45" s="3" t="str">
+        <f aca="false">NONCI_vgp!P45</f>
+        <v>0</v>
+      </c>
+      <c r="M45" s="3" t="str">
+        <f aca="false">NONCI_vgp!Q45</f>
+        <v>0</v>
+      </c>
+      <c r="N45" s="3" t="n">
+        <f aca="false">NONCI_vgp!R45</f>
+        <v>1</v>
+      </c>
+      <c r="O45" s="10" t="n">
+        <f aca="false">IF(K45=N45,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P45" s="1" t="n">
+        <f aca="false">IF(O45=1,N(N45),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R45" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P45), ISERROR(Q45), P45="NA", Q45="NA"),
+   "NA",
+   N(P45) + N(Q45)
+)</f>
         <v>1</v>
       </c>
     </row>
@@ -17271,16 +20068,44 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4143767531686,2.18247199757422","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I46" s="10" t="n">
-        <f aca="false">IF(NONCI_evt!R46=NONCI_vgp!R46,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J46" s="21" t="b">
-        <f aca="false">IF(I46=1, NONCI_evt!R46, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K46" s="21" t="b">
-        <f aca="false">IF(I46=1, NONCI_evt!R46, "")</f>
+      <c r="I46" s="3" t="str">
+        <f aca="false">NONCI_evt!P46</f>
+        <v>0</v>
+      </c>
+      <c r="J46" s="3" t="str">
+        <f aca="false">NONCI_evt!Q46</f>
+        <v>0</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <f aca="false">NONCI_evt!R46</f>
+        <v>1</v>
+      </c>
+      <c r="L46" s="3" t="str">
+        <f aca="false">NONCI_vgp!P46</f>
+        <v>0</v>
+      </c>
+      <c r="M46" s="3" t="str">
+        <f aca="false">NONCI_vgp!Q46</f>
+        <v>0</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <f aca="false">NONCI_vgp!R46</f>
+        <v>1</v>
+      </c>
+      <c r="O46" s="10" t="n">
+        <f aca="false">IF(K46=N46,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P46" s="1" t="n">
+        <f aca="false">IF(O46=1,N(N46),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R46" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P46), ISERROR(Q46), P46="NA", Q46="NA"),
+   "NA",
+   N(P46) + N(Q46)
+)</f>
         <v>1</v>
       </c>
     </row>
@@ -17311,16 +20136,44 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3829948804712,2.14940742253693","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I47" s="10" t="n">
-        <f aca="false">IF(NONCI_evt!R47=NONCI_vgp!R47,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J47" s="21" t="b">
-        <f aca="false">IF(I47=1, NONCI_evt!R47, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K47" s="21" t="b">
-        <f aca="false">IF(I47=1, NONCI_evt!R47, "")</f>
+      <c r="I47" s="3" t="str">
+        <f aca="false">NONCI_evt!P47</f>
+        <v>0</v>
+      </c>
+      <c r="J47" s="3" t="str">
+        <f aca="false">NONCI_evt!Q47</f>
+        <v>0</v>
+      </c>
+      <c r="K47" s="3" t="n">
+        <f aca="false">NONCI_evt!R47</f>
+        <v>1</v>
+      </c>
+      <c r="L47" s="3" t="str">
+        <f aca="false">NONCI_vgp!P47</f>
+        <v>0</v>
+      </c>
+      <c r="M47" s="3" t="str">
+        <f aca="false">NONCI_vgp!Q47</f>
+        <v>0</v>
+      </c>
+      <c r="N47" s="3" t="n">
+        <f aca="false">NONCI_vgp!R47</f>
+        <v>1</v>
+      </c>
+      <c r="O47" s="10" t="n">
+        <f aca="false">IF(K47=N47,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P47" s="1" t="n">
+        <f aca="false">IF(O47=1,N(N47),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R47" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P47), ISERROR(Q47), P47="NA", Q47="NA"),
+   "NA",
+   N(P47) + N(Q47)
+)</f>
         <v>1</v>
       </c>
     </row>
@@ -17351,16 +20204,44 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3773656033948,2.15472807927131","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I48" s="10" t="n">
-        <f aca="false">IF(NONCI_evt!R48=NONCI_vgp!R48,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J48" s="21" t="b">
-        <f aca="false">IF(I48=1, NONCI_evt!R48, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K48" s="21" t="b">
-        <f aca="false">IF(I48=1, NONCI_evt!R48, "")</f>
+      <c r="I48" s="3" t="str">
+        <f aca="false">NONCI_evt!P48</f>
+        <v>0</v>
+      </c>
+      <c r="J48" s="3" t="str">
+        <f aca="false">NONCI_evt!Q48</f>
+        <v>0</v>
+      </c>
+      <c r="K48" s="3" t="n">
+        <f aca="false">NONCI_evt!R48</f>
+        <v>1</v>
+      </c>
+      <c r="L48" s="3" t="str">
+        <f aca="false">NONCI_vgp!P48</f>
+        <v>0</v>
+      </c>
+      <c r="M48" s="3" t="str">
+        <f aca="false">NONCI_vgp!Q48</f>
+        <v>0</v>
+      </c>
+      <c r="N48" s="3" t="n">
+        <f aca="false">NONCI_vgp!R48</f>
+        <v>1</v>
+      </c>
+      <c r="O48" s="10" t="n">
+        <f aca="false">IF(K48=N48,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P48" s="1" t="n">
+        <f aca="false">IF(O48=1,N(N48),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R48" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P48), ISERROR(Q48), P48="NA", Q48="NA"),
+   "NA",
+   N(P48) + N(Q48)
+)</f>
         <v>1</v>
       </c>
     </row>
@@ -17391,16 +20272,44 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3828585874194,2.1482642373602","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I49" s="10" t="n">
-        <f aca="false">IF(NONCI_evt!R49=NONCI_vgp!R49,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J49" s="21" t="b">
-        <f aca="false">IF(I49=1, NONCI_evt!R49, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K49" s="21" t="b">
-        <f aca="false">IF(I49=1, NONCI_evt!R49, "")</f>
+      <c r="I49" s="3" t="str">
+        <f aca="false">NONCI_evt!P49</f>
+        <v>0</v>
+      </c>
+      <c r="J49" s="3" t="str">
+        <f aca="false">NONCI_evt!Q49</f>
+        <v>0</v>
+      </c>
+      <c r="K49" s="3" t="n">
+        <f aca="false">NONCI_evt!R49</f>
+        <v>1</v>
+      </c>
+      <c r="L49" s="3" t="str">
+        <f aca="false">NONCI_vgp!P49</f>
+        <v>0</v>
+      </c>
+      <c r="M49" s="3" t="str">
+        <f aca="false">NONCI_vgp!Q49</f>
+        <v>0</v>
+      </c>
+      <c r="N49" s="3" t="n">
+        <f aca="false">NONCI_vgp!R49</f>
+        <v>1</v>
+      </c>
+      <c r="O49" s="10" t="n">
+        <f aca="false">IF(K49=N49,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P49" s="1" t="n">
+        <f aca="false">IF(O49=1,N(N49),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R49" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P49), ISERROR(Q49), P49="NA", Q49="NA"),
+   "NA",
+   N(P49) + N(Q49)
+)</f>
         <v>1</v>
       </c>
     </row>
@@ -17431,16 +20340,44 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3776990081599,2.18875595645417","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I50" s="10" t="n">
-        <f aca="false">IF(NONCI_evt!R50=NONCI_vgp!R50,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J50" s="21" t="b">
-        <f aca="false">IF(I50=1, NONCI_evt!R50, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K50" s="21" t="b">
-        <f aca="false">IF(I50=1, NONCI_evt!R50, "")</f>
+      <c r="I50" s="3" t="str">
+        <f aca="false">NONCI_evt!P50</f>
+        <v>0</v>
+      </c>
+      <c r="J50" s="3" t="str">
+        <f aca="false">NONCI_evt!Q50</f>
+        <v>0</v>
+      </c>
+      <c r="K50" s="3" t="n">
+        <f aca="false">NONCI_evt!R50</f>
+        <v>1</v>
+      </c>
+      <c r="L50" s="3" t="str">
+        <f aca="false">NONCI_vgp!P50</f>
+        <v>0</v>
+      </c>
+      <c r="M50" s="3" t="str">
+        <f aca="false">NONCI_vgp!Q50</f>
+        <v>0</v>
+      </c>
+      <c r="N50" s="3" t="n">
+        <f aca="false">NONCI_vgp!R50</f>
+        <v>1</v>
+      </c>
+      <c r="O50" s="10" t="n">
+        <f aca="false">IF(K50=N50,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P50" s="1" t="n">
+        <f aca="false">IF(O50=1,N(N50),"")</f>
+        <v>1</v>
+      </c>
+      <c r="R50" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P50), ISERROR(Q50), P50="NA", Q50="NA"),
+   "NA",
+   N(P50) + N(Q50)
+)</f>
         <v>1</v>
       </c>
     </row>
@@ -17471,19 +20408,48 @@
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3799261629063,2.1592791307784","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I51" s="10" t="n">
-        <f aca="false">IF(NONCI_evt!R51=NONCI_vgp!R51,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J51" s="21" t="b">
-        <f aca="false">IF(I51=1, NONCI_evt!R51, "")</f>
-        <v>1</v>
-      </c>
-      <c r="K51" s="21" t="b">
-        <f aca="false">IF(I51=1, NONCI_evt!R51, "")</f>
-        <v>1</v>
-      </c>
-      <c r="L51" s="1"/>
+      <c r="I51" s="3" t="str">
+        <f aca="false">NONCI_evt!P51</f>
+        <v>0</v>
+      </c>
+      <c r="J51" s="3" t="str">
+        <f aca="false">NONCI_evt!Q51</f>
+        <v>0</v>
+      </c>
+      <c r="K51" s="3" t="n">
+        <f aca="false">NONCI_evt!R51</f>
+        <v>1</v>
+      </c>
+      <c r="L51" s="3" t="str">
+        <f aca="false">NONCI_vgp!P51</f>
+        <v>0</v>
+      </c>
+      <c r="M51" s="3" t="str">
+        <f aca="false">NONCI_vgp!Q51</f>
+        <v>0</v>
+      </c>
+      <c r="N51" s="3" t="n">
+        <f aca="false">NONCI_vgp!R51</f>
+        <v>1</v>
+      </c>
+      <c r="O51" s="10" t="n">
+        <f aca="false">IF(K51=N51,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P51" s="1" t="n">
+        <f aca="false">IF(O51=1,N(N51),"")</f>
+        <v>1</v>
+      </c>
+      <c r="Q51" s="1"/>
+      <c r="R51" s="1" t="n">
+        <f aca="false">IF(
+   OR(ISERROR(P51), ISERROR(Q51), P51="NA", Q51="NA"),
+   "NA",
+   N(P51) + N(Q51)
+)</f>
+        <v>1</v>
+      </c>
+      <c r="S51" s="1"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="10"/>
@@ -17494,16 +20460,22 @@
       <c r="F52" s="10"/>
       <c r="G52" s="10"/>
       <c r="H52" s="10"/>
-      <c r="I52" s="12" t="n">
-        <f aca="false">COUNTIFS(I3:I51,1)</f>
+      <c r="I52" s="10"/>
+      <c r="J52" s="10"/>
+      <c r="K52" s="10"/>
+      <c r="L52" s="10"/>
+      <c r="M52" s="10"/>
+      <c r="N52" s="10"/>
+      <c r="O52" s="12" t="n">
+        <f aca="false">COUNTIFS(O3:O51,1)</f>
         <v>43</v>
       </c>
-      <c r="J52" s="1" t="str">
-        <f aca="false">IF(I52=1, ADD_evt!R52, "")</f>
+      <c r="P52" s="1" t="str">
+        <f aca="false">IF(O52=1, ADD_evt!R52, "")</f>
         <v/>
       </c>
-      <c r="K52" s="12" t="n">
-        <f aca="false">COUNTIFS(K3:K51,1)</f>
+      <c r="R52" s="12" t="n">
+        <f aca="false">COUNTIFS(R3:R51,1)</f>
         <v>42</v>
       </c>
     </row>
@@ -17516,13 +20488,19 @@
       <c r="F53" s="10"/>
       <c r="G53" s="10"/>
       <c r="H53" s="10"/>
-      <c r="I53" s="22" t="n">
-        <f aca="false">COUNTIFS(I3:I51,1) / (COUNTIFS(I3:I51,1) + COUNTIFS(I3:I51,0))</f>
+      <c r="I53" s="10"/>
+      <c r="J53" s="10"/>
+      <c r="K53" s="10"/>
+      <c r="L53" s="10"/>
+      <c r="M53" s="10"/>
+      <c r="N53" s="10"/>
+      <c r="O53" s="22" t="n">
+        <f aca="false">COUNTIFS(O3:O51,1) / (COUNTIFS(O3:O51,1) + COUNTIFS(O3:O51,0))</f>
         <v>0.977272727272727</v>
       </c>
-      <c r="J53" s="22"/>
-      <c r="K53" s="23" t="n">
-        <f aca="false">COUNTIFS(K3:K51,1) / (COUNTIFS(K3:K51,1) + COUNTIFS(K3:K51,0))</f>
+      <c r="P53" s="22"/>
+      <c r="R53" s="23" t="n">
+        <f aca="false">COUNTIFS(R3:R51,1) / (COUNTIFS(R3:R51,1) + COUNTIFS(R3:R51,0))</f>
         <v>0.954545454545455</v>
       </c>
     </row>
@@ -17535,12 +20513,12 @@
       <c r="F54" s="10"/>
       <c r="G54" s="10"/>
       <c r="H54" s="10"/>
-      <c r="I54" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="K54" s="1" t="s">
-        <v>256</v>
-      </c>
+      <c r="I54" s="10"/>
+      <c r="J54" s="10"/>
+      <c r="K54" s="10"/>
+      <c r="L54" s="10"/>
+      <c r="M54" s="10"/>
+      <c r="N54" s="10"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
